--- a/data/folu_social_listening_report.xlsx
+++ b/data/folu_social_listening_report.xlsx
@@ -3016,12 +3016,12 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>curiosity_or_help_request</t>
+          <t>curiosity</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>question_or_information_seeking</t>
+          <t>technical_question_or_information_seeking</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -3031,7 +3031,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perhutanan sosial &amp; ekonomi karbon; Pertanyaan publik</t>
+          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perhutanan sosial &amp; ekonomi karbon; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -3131,7 +3131,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Deforestasi &amp; tata kelola hutan; Dukungan &amp; apresiasi; Pertanyaan publik</t>
+          <t>Deforestasi &amp; tata kelola hutan; Dukungan &amp; apresiasi; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O3" t="inlineStr"/>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Deforestasi &amp; tata kelola hutan; Dukungan &amp; apresiasi; Pertanyaan publik</t>
+          <t>Deforestasi &amp; tata kelola hutan; Dukungan &amp; apresiasi; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O4" t="inlineStr"/>
@@ -3519,7 +3519,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Edukasi FOLU Net Sink 2030; Program lapangan &amp; daerah; Dukungan &amp; apresiasi; Pertanyaan publik</t>
+          <t>Edukasi FOLU Net Sink 2030; Program lapangan &amp; daerah; Dukungan &amp; apresiasi; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -4262,12 +4262,12 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>curiosity_or_help_request</t>
+          <t>curiosity</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>question_or_information_seeking</t>
+          <t>technical_question_or_information_seeking</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -4277,7 +4277,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perhutanan sosial &amp; ekonomi karbon; Program lapangan &amp; daerah; Pertanyaan publik</t>
+          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perhutanan sosial &amp; ekonomi karbon; Program lapangan &amp; daerah; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -4362,12 +4362,12 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>curiosity_or_help_request</t>
+          <t>curiosity</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>question_or_information_seeking</t>
+          <t>technical_question_or_information_seeking</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -4377,7 +4377,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perhutanan sosial &amp; ekonomi karbon; Pertanyaan publik</t>
+          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perhutanan sosial &amp; ekonomi karbon; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -4654,12 +4654,12 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>curiosity_or_help_request</t>
+          <t>curiosity</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>question_or_information_seeking</t>
+          <t>technical_question_or_information_seeking</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Perubahan iklim &amp; emisi; Program lapangan &amp; daerah; Pertanyaan publik</t>
+          <t>Perubahan iklim &amp; emisi; Program lapangan &amp; daerah; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -4754,12 +4754,12 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>curiosity_or_help_request</t>
+          <t>curiosity</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>question_or_information_seeking</t>
+          <t>technical_question_or_information_seeking</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -4769,7 +4769,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Perubahan iklim &amp; emisi; Program lapangan &amp; daerah; Pertanyaan publik</t>
+          <t>Perubahan iklim &amp; emisi; Program lapangan &amp; daerah; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -5345,7 +5345,7 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>Deforestasi &amp; tata kelola hutan; Pertanyaan publik</t>
+          <t>Deforestasi &amp; tata kelola hutan; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -6006,12 +6006,12 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>curiosity_or_help_request</t>
+          <t>curiosity</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>question_or_information_seeking</t>
+          <t>technical_question_or_information_seeking</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -6021,7 +6021,7 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Pertanyaan publik</t>
+          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
@@ -6394,12 +6394,12 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>curiosity_or_help_request</t>
+          <t>curiosity</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>question_or_information_seeking</t>
+          <t>technical_question_or_information_seeking</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -6409,7 +6409,7 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perhutanan sosial &amp; ekonomi karbon; Pertanyaan publik</t>
+          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perhutanan sosial &amp; ekonomi karbon; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
@@ -6504,12 +6504,12 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Pertanyaan publik</t>
+          <t>Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>Pertanyaan publik</t>
+          <t>Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O38" t="inlineStr"/>
@@ -6600,12 +6600,12 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Pertanyaan publik</t>
+          <t>Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>Pertanyaan publik</t>
+          <t>Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O39" t="inlineStr"/>
@@ -6696,12 +6696,12 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Pertanyaan publik</t>
+          <t>Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>Pertanyaan publik</t>
+          <t>Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O40" t="inlineStr"/>
@@ -6792,12 +6792,12 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>Pertanyaan publik</t>
+          <t>Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>Pertanyaan publik</t>
+          <t>Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O41" t="inlineStr"/>
@@ -6888,12 +6888,12 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Pertanyaan publik</t>
+          <t>Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>Pertanyaan publik</t>
+          <t>Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O42" t="inlineStr"/>
@@ -6974,22 +6974,22 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>curiosity_or_help_request</t>
+          <t>curiosity</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>question_or_information_seeking</t>
+          <t>technical_question_or_information_seeking</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>Pertanyaan publik</t>
+          <t>Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>Pertanyaan publik</t>
+          <t>Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>Pertanyaan publik</t>
+          <t>Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>Pertanyaan publik</t>
+          <t>Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O44" t="inlineStr"/>
@@ -7170,22 +7170,22 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>curiosity_or_help_request</t>
+          <t>curiosity</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>question_or_information_seeking</t>
+          <t>technical_question_or_information_seeking</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>Pertanyaan publik</t>
+          <t>Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>Pertanyaan publik</t>
+          <t>Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
@@ -7270,12 +7270,12 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>curiosity_or_help_request</t>
+          <t>curiosity</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>question_or_information_seeking</t>
+          <t>technical_question_or_information_seeking</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -7285,7 +7285,7 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>Perhutanan sosial &amp; ekonomi karbon; Pertanyaan publik</t>
+          <t>Perhutanan sosial &amp; ekonomi karbon; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
@@ -7385,7 +7385,7 @@
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>Deforestasi &amp; tata kelola hutan; Pertanyaan publik</t>
+          <t>Deforestasi &amp; tata kelola hutan; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O47" t="inlineStr"/>
@@ -7481,7 +7481,7 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>Edukasi FOLU Net Sink 2030; Pertanyaan publik</t>
+          <t>Edukasi FOLU Net Sink 2030; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O48" t="inlineStr"/>
@@ -7577,7 +7577,7 @@
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>Edukasi FOLU Net Sink 2030; Pertanyaan publik</t>
+          <t>Edukasi FOLU Net Sink 2030; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O49" t="inlineStr"/>
@@ -8119,7 +8119,7 @@
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Pertanyaan publik</t>
+          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O55" t="inlineStr"/>
@@ -8209,7 +8209,7 @@
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Pertanyaan publik</t>
+          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O56" t="inlineStr"/>
@@ -8299,7 +8299,7 @@
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Pertanyaan publik</t>
+          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O57" t="inlineStr"/>
@@ -8366,7 +8366,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>negative</t>
+          <t>aspiration</t>
         </is>
       </c>
       <c r="J58" t="n">
@@ -8374,12 +8374,12 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>concern</t>
+          <t>hope_or_urgent_public_request</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>critical_or_concern</t>
+          <t>public_expectation_or_action_request</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
@@ -8389,10 +8389,14 @@
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Pertanyaan publik</t>
-        </is>
-      </c>
-      <c r="O58" t="inlineStr"/>
+          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Aspirasi &amp; permintaan tindak lanjut; Pertanyaan teknis publik</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>public_aspiration_needs_response</t>
+        </is>
+      </c>
       <c r="P58" t="b">
         <v>0</v>
       </c>
@@ -8415,7 +8419,7 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>negative</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -8464,12 +8468,12 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>curiosity_or_help_request</t>
+          <t>curiosity</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>question_or_information_seeking</t>
+          <t>technical_question_or_information_seeking</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
@@ -8479,7 +8483,7 @@
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Pertanyaan publik</t>
+          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
@@ -8550,7 +8554,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>question</t>
         </is>
       </c>
       <c r="J60" t="n">
@@ -8558,12 +8562,12 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>curiosity</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>neutral_or_unclear</t>
+          <t>technical_question_or_information_seeking</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
@@ -8573,7 +8577,7 @@
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Pertanyaan publik</t>
+          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
@@ -8652,12 +8656,12 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>curiosity_or_help_request</t>
+          <t>curiosity</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>question_or_information_seeking</t>
+          <t>technical_question_or_information_seeking</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
@@ -8667,7 +8671,7 @@
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Pertanyaan publik</t>
+          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
@@ -8761,7 +8765,7 @@
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Pertanyaan publik</t>
+          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O62" t="inlineStr"/>
@@ -9466,12 +9470,12 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>curiosity_or_help_request</t>
+          <t>curiosity</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>question_or_information_seeking</t>
+          <t>technical_question_or_information_seeking</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -9481,7 +9485,7 @@
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>Edukasi FOLU Net Sink 2030; Perhutanan sosial &amp; ekonomi karbon; Pertanyaan publik</t>
+          <t>Edukasi FOLU Net Sink 2030; Perhutanan sosial &amp; ekonomi karbon; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
@@ -9575,7 +9579,7 @@
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>Edukasi FOLU Net Sink 2030; Pertanyaan publik</t>
+          <t>Edukasi FOLU Net Sink 2030; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
@@ -10558,12 +10562,12 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>curiosity_or_help_request</t>
+          <t>curiosity</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>question_or_information_seeking</t>
+          <t>technical_question_or_information_seeking</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
@@ -10573,7 +10577,7 @@
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Pertanyaan publik</t>
+          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O82" t="inlineStr">
@@ -10644,7 +10648,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>question</t>
+          <t>aspiration</t>
         </is>
       </c>
       <c r="J83" t="n">
@@ -10652,12 +10656,12 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>curiosity_or_help_request</t>
+          <t>hope_or_urgent_public_request</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>question_or_information_seeking</t>
+          <t>public_expectation_or_action_request</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
@@ -10667,12 +10671,12 @@
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030</t>
+          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Aspirasi &amp; permintaan tindak lanjut</t>
         </is>
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>deforestation_criticism</t>
+          <t>deforestation_criticism; public_aspiration_needs_response</t>
         </is>
       </c>
       <c r="P83" t="b">
@@ -10836,12 +10840,12 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>curiosity_or_help_request</t>
+          <t>curiosity</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>question_or_information_seeking</t>
+          <t>technical_question_or_information_seeking</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
@@ -10851,7 +10855,7 @@
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>Edukasi FOLU Net Sink 2030; Pertanyaan publik</t>
+          <t>Edukasi FOLU Net Sink 2030; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O85" t="inlineStr">
@@ -11110,12 +11114,12 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>curiosity_or_help_request</t>
+          <t>curiosity</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>question_or_information_seeking</t>
+          <t>technical_question_or_information_seeking</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
@@ -11125,7 +11129,7 @@
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Pertanyaan publik</t>
+          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O88" t="inlineStr">
@@ -12274,12 +12278,12 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>curiosity_or_help_request</t>
+          <t>curiosity</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>question_or_information_seeking</t>
+          <t>technical_question_or_information_seeking</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
@@ -12289,7 +12293,7 @@
       </c>
       <c r="N101" t="inlineStr">
         <is>
-          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Pertanyaan publik</t>
+          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O101" t="inlineStr">
@@ -12383,7 +12387,7 @@
       </c>
       <c r="N102" t="inlineStr">
         <is>
-          <t>Edukasi FOLU Net Sink 2030; Pertanyaan publik</t>
+          <t>Edukasi FOLU Net Sink 2030; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O102" t="inlineStr"/>
@@ -12473,7 +12477,7 @@
       </c>
       <c r="N103" t="inlineStr">
         <is>
-          <t>Edukasi FOLU Net Sink 2030; Pertanyaan publik</t>
+          <t>Edukasi FOLU Net Sink 2030; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O103" t="inlineStr"/>
@@ -12563,7 +12567,7 @@
       </c>
       <c r="N104" t="inlineStr">
         <is>
-          <t>Edukasi FOLU Net Sink 2030; Pertanyaan publik</t>
+          <t>Edukasi FOLU Net Sink 2030; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O104" t="inlineStr"/>
@@ -12653,7 +12657,7 @@
       </c>
       <c r="N105" t="inlineStr">
         <is>
-          <t>Edukasi FOLU Net Sink 2030; Dukungan &amp; apresiasi; Pertanyaan publik</t>
+          <t>Edukasi FOLU Net Sink 2030; Dukungan &amp; apresiasi; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O105" t="inlineStr"/>
@@ -12720,7 +12724,7 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>question</t>
         </is>
       </c>
       <c r="J106" t="n">
@@ -12728,12 +12732,12 @@
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>curiosity</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>neutral_or_unclear</t>
+          <t>technical_question_or_information_seeking</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
@@ -12743,7 +12747,7 @@
       </c>
       <c r="N106" t="inlineStr">
         <is>
-          <t>Edukasi FOLU Net Sink 2030; Pertanyaan publik</t>
+          <t>Edukasi FOLU Net Sink 2030; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O106" t="inlineStr">
@@ -12814,7 +12818,7 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>question</t>
+          <t>aspiration</t>
         </is>
       </c>
       <c r="J107" t="n">
@@ -12822,12 +12826,12 @@
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>curiosity_or_help_request</t>
+          <t>hope_or_urgent_public_request</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>question_or_information_seeking</t>
+          <t>public_expectation_or_action_request</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
@@ -12837,7 +12841,7 @@
       </c>
       <c r="N107" t="inlineStr">
         <is>
-          <t>Edukasi FOLU Net Sink 2030; Pertanyaan publik</t>
+          <t>Edukasi FOLU Net Sink 2030; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O107" t="inlineStr">
@@ -12931,7 +12935,7 @@
       </c>
       <c r="N108" t="inlineStr">
         <is>
-          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Pertanyaan publik</t>
+          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O108" t="inlineStr"/>
@@ -13814,7 +13818,7 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>question</t>
+          <t>aspiration</t>
         </is>
       </c>
       <c r="J118" t="n">
@@ -13822,12 +13826,12 @@
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>curiosity_or_help_request</t>
+          <t>hope_or_urgent_public_request</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>question_or_information_seeking</t>
+          <t>public_expectation_or_action_request</t>
         </is>
       </c>
       <c r="M118" t="inlineStr">
@@ -13837,10 +13841,14 @@
       </c>
       <c r="N118" t="inlineStr">
         <is>
-          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Program lapangan &amp; daerah</t>
-        </is>
-      </c>
-      <c r="O118" t="inlineStr"/>
+          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Program lapangan &amp; daerah; Aspirasi &amp; permintaan tindak lanjut</t>
+        </is>
+      </c>
+      <c r="O118" t="inlineStr">
+        <is>
+          <t>public_aspiration_needs_response</t>
+        </is>
+      </c>
       <c r="P118" t="b">
         <v>0</v>
       </c>
@@ -13924,12 +13932,12 @@
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>curiosity_or_help_request</t>
+          <t>curiosity</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>question_or_information_seeking</t>
+          <t>technical_question_or_information_seeking</t>
         </is>
       </c>
       <c r="M119" t="inlineStr">
@@ -14030,12 +14038,12 @@
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>curiosity_or_help_request</t>
+          <t>curiosity</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>question_or_information_seeking</t>
+          <t>technical_question_or_information_seeking</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
@@ -14045,7 +14053,7 @@
       </c>
       <c r="N120" t="inlineStr">
         <is>
-          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Program lapangan &amp; daerah; Pertanyaan publik</t>
+          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Program lapangan &amp; daerah; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O120" t="inlineStr">
@@ -14238,12 +14246,12 @@
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>curiosity_or_help_request</t>
+          <t>curiosity</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>question_or_information_seeking</t>
+          <t>technical_question_or_information_seeking</t>
         </is>
       </c>
       <c r="M122" t="inlineStr">
@@ -14253,7 +14261,7 @@
       </c>
       <c r="N122" t="inlineStr">
         <is>
-          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Program lapangan &amp; daerah; Pertanyaan publik</t>
+          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Program lapangan &amp; daerah; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O122" t="inlineStr">
@@ -14652,12 +14660,12 @@
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>curiosity_or_help_request</t>
+          <t>curiosity</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>question_or_information_seeking</t>
+          <t>technical_question_or_information_seeking</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
@@ -14667,7 +14675,7 @@
       </c>
       <c r="N126" t="inlineStr">
         <is>
-          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Program lapangan &amp; daerah; Pertanyaan publik</t>
+          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Program lapangan &amp; daerah; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O126" t="inlineStr">
@@ -14773,7 +14781,7 @@
       </c>
       <c r="N127" t="inlineStr">
         <is>
-          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Program lapangan &amp; daerah; Pertanyaan publik</t>
+          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Program lapangan &amp; daerah; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O127" t="inlineStr">
@@ -15083,7 +15091,7 @@
       </c>
       <c r="N130" t="inlineStr">
         <is>
-          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perhutanan sosial &amp; ekonomi karbon; Program lapangan &amp; daerah; Pertanyaan publik</t>
+          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perhutanan sosial &amp; ekonomi karbon; Program lapangan &amp; daerah; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O130" t="inlineStr">
@@ -15368,7 +15376,7 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>question</t>
         </is>
       </c>
       <c r="J133" t="n">
@@ -15376,12 +15384,12 @@
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>curiosity</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>neutral_or_unclear</t>
+          <t>technical_question_or_information_seeking</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
@@ -15391,7 +15399,7 @@
       </c>
       <c r="N133" t="inlineStr">
         <is>
-          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Program lapangan &amp; daerah; Pertanyaan publik</t>
+          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Program lapangan &amp; daerah; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O133" t="inlineStr">
@@ -15482,12 +15490,12 @@
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>curiosity_or_help_request</t>
+          <t>curiosity</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>question_or_information_seeking</t>
+          <t>technical_question_or_information_seeking</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
@@ -15497,7 +15505,7 @@
       </c>
       <c r="N134" t="inlineStr">
         <is>
-          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Program lapangan &amp; daerah; Pertanyaan publik</t>
+          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Program lapangan &amp; daerah; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O134" t="inlineStr">
@@ -16296,7 +16304,7 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>positive</t>
+          <t>question</t>
         </is>
       </c>
       <c r="J142" t="n">
@@ -16304,12 +16312,12 @@
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>appreciation</t>
+          <t>curiosity</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>supportive_or_appreciative</t>
+          <t>technical_question_or_information_seeking</t>
         </is>
       </c>
       <c r="M142" t="inlineStr">
@@ -16319,7 +16327,7 @@
       </c>
       <c r="N142" t="inlineStr">
         <is>
-          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Program lapangan &amp; daerah; Pertanyaan publik</t>
+          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Program lapangan &amp; daerah; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O142" t="inlineStr">
@@ -16357,7 +16365,7 @@
       </c>
       <c r="X142" t="inlineStr">
         <is>
-          <t>positive</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -16512,12 +16520,12 @@
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>curiosity_or_help_request</t>
+          <t>curiosity</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>question_or_information_seeking</t>
+          <t>technical_question_or_information_seeking</t>
         </is>
       </c>
       <c r="M144" t="inlineStr">
@@ -16527,7 +16535,7 @@
       </c>
       <c r="N144" t="inlineStr">
         <is>
-          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Program lapangan &amp; daerah; Pertanyaan publik</t>
+          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Program lapangan &amp; daerah; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O144" t="inlineStr">
@@ -17436,12 +17444,12 @@
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>curiosity_or_help_request</t>
+          <t>curiosity</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>question_or_information_seeking</t>
+          <t>technical_question_or_information_seeking</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
@@ -17451,7 +17459,7 @@
       </c>
       <c r="N153" t="inlineStr">
         <is>
-          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Program lapangan &amp; daerah; Pertanyaan publik</t>
+          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Program lapangan &amp; daerah; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O153" t="inlineStr">
@@ -18140,7 +18148,7 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>question</t>
+          <t>aspiration</t>
         </is>
       </c>
       <c r="J160" t="n">
@@ -18148,12 +18156,12 @@
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>curiosity_or_help_request</t>
+          <t>hope_or_urgent_public_request</t>
         </is>
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t>question_or_information_seeking</t>
+          <t>public_expectation_or_action_request</t>
         </is>
       </c>
       <c r="M160" t="inlineStr">
@@ -18163,10 +18171,14 @@
       </c>
       <c r="N160" t="inlineStr">
         <is>
-          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Program lapangan &amp; daerah</t>
-        </is>
-      </c>
-      <c r="O160" t="inlineStr"/>
+          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Program lapangan &amp; daerah; Aspirasi &amp; permintaan tindak lanjut</t>
+        </is>
+      </c>
+      <c r="O160" t="inlineStr">
+        <is>
+          <t>public_aspiration_needs_response</t>
+        </is>
+      </c>
       <c r="P160" t="b">
         <v>0</v>
       </c>
@@ -18350,12 +18362,12 @@
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t>curiosity_or_help_request</t>
+          <t>curiosity</t>
         </is>
       </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t>question_or_information_seeking</t>
+          <t>technical_question_or_information_seeking</t>
         </is>
       </c>
       <c r="M162" t="inlineStr">
@@ -18365,7 +18377,7 @@
       </c>
       <c r="N162" t="inlineStr">
         <is>
-          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Program lapangan &amp; daerah; Pertanyaan publik</t>
+          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Program lapangan &amp; daerah; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O162" t="inlineStr">
@@ -18856,12 +18868,12 @@
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t>curiosity_or_help_request</t>
+          <t>curiosity</t>
         </is>
       </c>
       <c r="L167" t="inlineStr">
         <is>
-          <t>question_or_information_seeking</t>
+          <t>technical_question_or_information_seeking</t>
         </is>
       </c>
       <c r="M167" t="inlineStr">
@@ -18871,7 +18883,7 @@
       </c>
       <c r="N167" t="inlineStr">
         <is>
-          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Program lapangan &amp; daerah; Pertanyaan publik</t>
+          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Program lapangan &amp; daerah; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O167" t="inlineStr">
@@ -19075,7 +19087,7 @@
       </c>
       <c r="N169" t="inlineStr">
         <is>
-          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perhutanan sosial &amp; ekonomi karbon; Program lapangan &amp; daerah; Pertanyaan publik</t>
+          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perhutanan sosial &amp; ekonomi karbon; Program lapangan &amp; daerah; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O169" t="inlineStr">
@@ -19468,12 +19480,12 @@
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t>curiosity_or_help_request</t>
+          <t>curiosity</t>
         </is>
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>question_or_information_seeking</t>
+          <t>technical_question_or_information_seeking</t>
         </is>
       </c>
       <c r="M173" t="inlineStr">
@@ -19483,7 +19495,7 @@
       </c>
       <c r="N173" t="inlineStr">
         <is>
-          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Program lapangan &amp; daerah; Pertanyaan publik</t>
+          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Program lapangan &amp; daerah; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O173" t="inlineStr">
@@ -19574,12 +19586,12 @@
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t>curiosity_or_help_request</t>
+          <t>curiosity</t>
         </is>
       </c>
       <c r="L174" t="inlineStr">
         <is>
-          <t>question_or_information_seeking</t>
+          <t>technical_question_or_information_seeking</t>
         </is>
       </c>
       <c r="M174" t="inlineStr">
@@ -19589,7 +19601,7 @@
       </c>
       <c r="N174" t="inlineStr">
         <is>
-          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Program lapangan &amp; daerah; Pertanyaan publik</t>
+          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Program lapangan &amp; daerah; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O174" t="inlineStr">
@@ -19982,12 +19994,12 @@
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t>curiosity_or_help_request</t>
+          <t>curiosity</t>
         </is>
       </c>
       <c r="L178" t="inlineStr">
         <is>
-          <t>question_or_information_seeking</t>
+          <t>technical_question_or_information_seeking</t>
         </is>
       </c>
       <c r="M178" t="inlineStr">
@@ -19997,7 +20009,7 @@
       </c>
       <c r="N178" t="inlineStr">
         <is>
-          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Program lapangan &amp; daerah; Pertanyaan publik</t>
+          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Program lapangan &amp; daerah; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O178" t="inlineStr">
@@ -20594,12 +20606,12 @@
       </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t>curiosity_or_help_request</t>
+          <t>curiosity</t>
         </is>
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>question_or_information_seeking</t>
+          <t>technical_question_or_information_seeking</t>
         </is>
       </c>
       <c r="M184" t="inlineStr">
@@ -20609,7 +20621,7 @@
       </c>
       <c r="N184" t="inlineStr">
         <is>
-          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Program lapangan &amp; daerah; Pertanyaan publik</t>
+          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Program lapangan &amp; daerah; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O184" t="inlineStr">
@@ -20700,12 +20712,12 @@
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t>curiosity_or_help_request</t>
+          <t>curiosity</t>
         </is>
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>question_or_information_seeking</t>
+          <t>technical_question_or_information_seeking</t>
         </is>
       </c>
       <c r="M185" t="inlineStr">
@@ -20715,7 +20727,7 @@
       </c>
       <c r="N185" t="inlineStr">
         <is>
-          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Program lapangan &amp; daerah; Pertanyaan publik</t>
+          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Program lapangan &amp; daerah; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O185" t="inlineStr">
@@ -20908,12 +20920,12 @@
       </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t>curiosity_or_help_request</t>
+          <t>curiosity</t>
         </is>
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t>question_or_information_seeking</t>
+          <t>technical_question_or_information_seeking</t>
         </is>
       </c>
       <c r="M187" t="inlineStr">
@@ -20923,7 +20935,7 @@
       </c>
       <c r="N187" t="inlineStr">
         <is>
-          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Program lapangan &amp; daerah; Pertanyaan publik</t>
+          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Program lapangan &amp; daerah; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O187" t="inlineStr">
@@ -21004,7 +21016,7 @@
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>question</t>
         </is>
       </c>
       <c r="J188" t="n">
@@ -21012,12 +21024,12 @@
       </c>
       <c r="K188" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>curiosity</t>
         </is>
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t>neutral_or_unclear</t>
+          <t>technical_question_or_information_seeking</t>
         </is>
       </c>
       <c r="M188" t="inlineStr">
@@ -21027,7 +21039,7 @@
       </c>
       <c r="N188" t="inlineStr">
         <is>
-          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Program lapangan &amp; daerah; Pertanyaan publik</t>
+          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Program lapangan &amp; daerah; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O188" t="inlineStr">
@@ -21418,12 +21430,12 @@
       </c>
       <c r="K192" t="inlineStr">
         <is>
-          <t>curiosity_or_help_request</t>
+          <t>curiosity</t>
         </is>
       </c>
       <c r="L192" t="inlineStr">
         <is>
-          <t>question_or_information_seeking</t>
+          <t>technical_question_or_information_seeking</t>
         </is>
       </c>
       <c r="M192" t="inlineStr">
@@ -21433,7 +21445,7 @@
       </c>
       <c r="N192" t="inlineStr">
         <is>
-          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Program lapangan &amp; daerah; Pertanyaan publik</t>
+          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Program lapangan &amp; daerah; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O192" t="inlineStr">
@@ -21722,12 +21734,12 @@
       </c>
       <c r="K195" t="inlineStr">
         <is>
-          <t>curiosity_or_help_request</t>
+          <t>curiosity</t>
         </is>
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t>question_or_information_seeking</t>
+          <t>technical_question_or_information_seeking</t>
         </is>
       </c>
       <c r="M195" t="inlineStr">
@@ -21737,7 +21749,7 @@
       </c>
       <c r="N195" t="inlineStr">
         <is>
-          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Program lapangan &amp; daerah; Pertanyaan publik</t>
+          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Program lapangan &amp; daerah; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O195" t="inlineStr">
@@ -22230,12 +22242,12 @@
       </c>
       <c r="K200" t="inlineStr">
         <is>
-          <t>curiosity_or_help_request</t>
+          <t>curiosity</t>
         </is>
       </c>
       <c r="L200" t="inlineStr">
         <is>
-          <t>question_or_information_seeking</t>
+          <t>technical_question_or_information_seeking</t>
         </is>
       </c>
       <c r="M200" t="inlineStr">
@@ -22245,7 +22257,7 @@
       </c>
       <c r="N200" t="inlineStr">
         <is>
-          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Program lapangan &amp; daerah; Pertanyaan publik</t>
+          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Program lapangan &amp; daerah; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O200" t="inlineStr">
@@ -22526,7 +22538,7 @@
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>aspiration</t>
         </is>
       </c>
       <c r="J203" t="n">
@@ -22534,12 +22546,12 @@
       </c>
       <c r="K203" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>hope_or_urgent_public_request</t>
         </is>
       </c>
       <c r="L203" t="inlineStr">
         <is>
-          <t>neutral_or_unclear</t>
+          <t>public_expectation_or_action_request</t>
         </is>
       </c>
       <c r="M203" t="inlineStr">
@@ -23328,7 +23340,7 @@
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t>question</t>
+          <t>aspiration</t>
         </is>
       </c>
       <c r="J211" t="n">
@@ -23336,12 +23348,12 @@
       </c>
       <c r="K211" t="inlineStr">
         <is>
-          <t>curiosity_or_help_request</t>
+          <t>hope_or_urgent_public_request</t>
         </is>
       </c>
       <c r="L211" t="inlineStr">
         <is>
-          <t>question_or_information_seeking</t>
+          <t>public_expectation_or_action_request</t>
         </is>
       </c>
       <c r="M211" t="inlineStr">
@@ -23351,10 +23363,14 @@
       </c>
       <c r="N211" t="inlineStr">
         <is>
-          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Program lapangan &amp; daerah</t>
-        </is>
-      </c>
-      <c r="O211" t="inlineStr"/>
+          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Program lapangan &amp; daerah; Aspirasi &amp; permintaan tindak lanjut</t>
+        </is>
+      </c>
+      <c r="O211" t="inlineStr">
+        <is>
+          <t>public_aspiration_needs_response</t>
+        </is>
+      </c>
       <c r="P211" t="b">
         <v>0</v>
       </c>
@@ -23436,12 +23452,12 @@
       </c>
       <c r="K212" t="inlineStr">
         <is>
-          <t>curiosity_or_help_request</t>
+          <t>curiosity</t>
         </is>
       </c>
       <c r="L212" t="inlineStr">
         <is>
-          <t>question_or_information_seeking</t>
+          <t>technical_question_or_information_seeking</t>
         </is>
       </c>
       <c r="M212" t="inlineStr">
@@ -23451,7 +23467,7 @@
       </c>
       <c r="N212" t="inlineStr">
         <is>
-          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Program lapangan &amp; daerah; Pertanyaan publik</t>
+          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Program lapangan &amp; daerah; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O212" t="inlineStr">
@@ -25257,7 +25273,7 @@
       </c>
       <c r="N230" t="inlineStr">
         <is>
-          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Program lapangan &amp; daerah; Pertanyaan publik</t>
+          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Program lapangan &amp; daerah; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O230" t="inlineStr">
@@ -25348,12 +25364,12 @@
       </c>
       <c r="K231" t="inlineStr">
         <is>
-          <t>curiosity_or_help_request</t>
+          <t>curiosity</t>
         </is>
       </c>
       <c r="L231" t="inlineStr">
         <is>
-          <t>question_or_information_seeking</t>
+          <t>technical_question_or_information_seeking</t>
         </is>
       </c>
       <c r="M231" t="inlineStr">
@@ -25554,12 +25570,12 @@
       </c>
       <c r="K233" t="inlineStr">
         <is>
-          <t>curiosity_or_help_request</t>
+          <t>curiosity</t>
         </is>
       </c>
       <c r="L233" t="inlineStr">
         <is>
-          <t>question_or_information_seeking</t>
+          <t>technical_question_or_information_seeking</t>
         </is>
       </c>
       <c r="M233" t="inlineStr">
@@ -25569,7 +25585,7 @@
       </c>
       <c r="N233" t="inlineStr">
         <is>
-          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Program lapangan &amp; daerah; Pertanyaan publik</t>
+          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Program lapangan &amp; daerah; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O233" t="inlineStr">
@@ -25658,12 +25674,12 @@
       </c>
       <c r="K234" t="inlineStr">
         <is>
-          <t>curiosity_or_help_request</t>
+          <t>curiosity</t>
         </is>
       </c>
       <c r="L234" t="inlineStr">
         <is>
-          <t>question_or_information_seeking</t>
+          <t>technical_question_or_information_seeking</t>
         </is>
       </c>
       <c r="M234" t="inlineStr">
@@ -25673,7 +25689,7 @@
       </c>
       <c r="N234" t="inlineStr">
         <is>
-          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Program lapangan &amp; daerah; Pertanyaan publik</t>
+          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Program lapangan &amp; daerah; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O234" t="inlineStr">
@@ -25762,12 +25778,12 @@
       </c>
       <c r="K235" t="inlineStr">
         <is>
-          <t>curiosity_or_help_request</t>
+          <t>curiosity</t>
         </is>
       </c>
       <c r="L235" t="inlineStr">
         <is>
-          <t>question_or_information_seeking</t>
+          <t>technical_question_or_information_seeking</t>
         </is>
       </c>
       <c r="M235" t="inlineStr">
@@ -25777,7 +25793,7 @@
       </c>
       <c r="N235" t="inlineStr">
         <is>
-          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Program lapangan &amp; daerah; Pertanyaan publik</t>
+          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Program lapangan &amp; daerah; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O235" t="inlineStr">
@@ -25958,7 +25974,7 @@
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t>question</t>
+          <t>aspiration</t>
         </is>
       </c>
       <c r="J237" t="n">
@@ -25966,12 +25982,12 @@
       </c>
       <c r="K237" t="inlineStr">
         <is>
-          <t>curiosity_or_help_request</t>
+          <t>hope_or_urgent_public_request</t>
         </is>
       </c>
       <c r="L237" t="inlineStr">
         <is>
-          <t>question_or_information_seeking</t>
+          <t>public_expectation_or_action_request</t>
         </is>
       </c>
       <c r="M237" t="inlineStr">
@@ -25981,10 +25997,14 @@
       </c>
       <c r="N237" t="inlineStr">
         <is>
-          <t>Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Pertanyaan publik</t>
-        </is>
-      </c>
-      <c r="O237" t="inlineStr"/>
+          <t>Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Aspirasi &amp; permintaan tindak lanjut; Pertanyaan teknis publik</t>
+        </is>
+      </c>
+      <c r="O237" t="inlineStr">
+        <is>
+          <t>public_aspiration_needs_response</t>
+        </is>
+      </c>
       <c r="P237" t="b">
         <v>0</v>
       </c>
@@ -26083,7 +26103,7 @@
       </c>
       <c r="N238" t="inlineStr">
         <is>
-          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Pertanyaan publik</t>
+          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O238" t="inlineStr"/>
@@ -26162,7 +26182,7 @@
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t>question</t>
+          <t>aspiration</t>
         </is>
       </c>
       <c r="J239" t="n">
@@ -26170,12 +26190,12 @@
       </c>
       <c r="K239" t="inlineStr">
         <is>
-          <t>curiosity_or_help_request</t>
+          <t>hope_or_urgent_public_request</t>
         </is>
       </c>
       <c r="L239" t="inlineStr">
         <is>
-          <t>question_or_information_seeking</t>
+          <t>public_expectation_or_action_request</t>
         </is>
       </c>
       <c r="M239" t="inlineStr">
@@ -26185,10 +26205,14 @@
       </c>
       <c r="N239" t="inlineStr">
         <is>
-          <t>Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Pertanyaan publik</t>
-        </is>
-      </c>
-      <c r="O239" t="inlineStr"/>
+          <t>Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Aspirasi &amp; permintaan tindak lanjut; Pertanyaan teknis publik</t>
+        </is>
+      </c>
+      <c r="O239" t="inlineStr">
+        <is>
+          <t>public_aspiration_needs_response</t>
+        </is>
+      </c>
       <c r="P239" t="b">
         <v>0</v>
       </c>
@@ -26285,7 +26309,7 @@
       </c>
       <c r="N240" t="inlineStr">
         <is>
-          <t>Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Pertanyaan publik</t>
+          <t>Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O240" t="inlineStr"/>
@@ -26364,7 +26388,7 @@
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t>question</t>
+          <t>aspiration</t>
         </is>
       </c>
       <c r="J241" t="n">
@@ -26372,12 +26396,12 @@
       </c>
       <c r="K241" t="inlineStr">
         <is>
-          <t>curiosity_or_help_request</t>
+          <t>hope_or_urgent_public_request</t>
         </is>
       </c>
       <c r="L241" t="inlineStr">
         <is>
-          <t>question_or_information_seeking</t>
+          <t>public_expectation_or_action_request</t>
         </is>
       </c>
       <c r="M241" t="inlineStr">
@@ -26387,10 +26411,14 @@
       </c>
       <c r="N241" t="inlineStr">
         <is>
-          <t>Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Pertanyaan publik</t>
-        </is>
-      </c>
-      <c r="O241" t="inlineStr"/>
+          <t>Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Aspirasi &amp; permintaan tindak lanjut; Pertanyaan teknis publik</t>
+        </is>
+      </c>
+      <c r="O241" t="inlineStr">
+        <is>
+          <t>public_aspiration_needs_response</t>
+        </is>
+      </c>
       <c r="P241" t="b">
         <v>0</v>
       </c>
@@ -26474,12 +26502,12 @@
       </c>
       <c r="K242" t="inlineStr">
         <is>
-          <t>curiosity_or_help_request</t>
+          <t>curiosity</t>
         </is>
       </c>
       <c r="L242" t="inlineStr">
         <is>
-          <t>question_or_information_seeking</t>
+          <t>technical_question_or_information_seeking</t>
         </is>
       </c>
       <c r="M242" t="inlineStr">
@@ -26489,7 +26517,7 @@
       </c>
       <c r="N242" t="inlineStr">
         <is>
-          <t>Konflik lahan &amp; hutan lindung; Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Pertanyaan publik</t>
+          <t>Konflik lahan &amp; hutan lindung; Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O242" t="inlineStr">
@@ -26593,7 +26621,7 @@
       </c>
       <c r="N243" t="inlineStr">
         <is>
-          <t>Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Pertanyaan publik</t>
+          <t>Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O243" t="inlineStr"/>
@@ -26693,7 +26721,7 @@
       </c>
       <c r="N244" t="inlineStr">
         <is>
-          <t>Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Pertanyaan publik</t>
+          <t>Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O244" t="inlineStr"/>
@@ -26795,7 +26823,7 @@
       </c>
       <c r="N245" t="inlineStr">
         <is>
-          <t>Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Pertanyaan publik</t>
+          <t>Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O245" t="inlineStr"/>
@@ -26895,7 +26923,7 @@
       </c>
       <c r="N246" t="inlineStr">
         <is>
-          <t>Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Pertanyaan publik</t>
+          <t>Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O246" t="inlineStr">
@@ -26984,12 +27012,12 @@
       </c>
       <c r="K247" t="inlineStr">
         <is>
-          <t>curiosity_or_help_request</t>
+          <t>curiosity</t>
         </is>
       </c>
       <c r="L247" t="inlineStr">
         <is>
-          <t>question_or_information_seeking</t>
+          <t>technical_question_or_information_seeking</t>
         </is>
       </c>
       <c r="M247" t="inlineStr">
@@ -26999,7 +27027,7 @@
       </c>
       <c r="N247" t="inlineStr">
         <is>
-          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Pertanyaan publik</t>
+          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O247" t="inlineStr">
@@ -27082,7 +27110,7 @@
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t>question</t>
+          <t>aspiration</t>
         </is>
       </c>
       <c r="J248" t="n">
@@ -27090,12 +27118,12 @@
       </c>
       <c r="K248" t="inlineStr">
         <is>
-          <t>curiosity_or_help_request</t>
+          <t>hope_or_urgent_public_request</t>
         </is>
       </c>
       <c r="L248" t="inlineStr">
         <is>
-          <t>question_or_information_seeking</t>
+          <t>public_expectation_or_action_request</t>
         </is>
       </c>
       <c r="M248" t="inlineStr">
@@ -27105,10 +27133,14 @@
       </c>
       <c r="N248" t="inlineStr">
         <is>
-          <t>Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Pertanyaan publik</t>
-        </is>
-      </c>
-      <c r="O248" t="inlineStr"/>
+          <t>Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Aspirasi &amp; permintaan tindak lanjut; Pertanyaan teknis publik</t>
+        </is>
+      </c>
+      <c r="O248" t="inlineStr">
+        <is>
+          <t>public_aspiration_needs_response</t>
+        </is>
+      </c>
       <c r="P248" t="b">
         <v>0</v>
       </c>
@@ -27207,7 +27239,7 @@
       </c>
       <c r="N249" t="inlineStr">
         <is>
-          <t>Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Pertanyaan publik</t>
+          <t>Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O249" t="inlineStr"/>
@@ -27284,7 +27316,7 @@
       </c>
       <c r="I250" t="inlineStr">
         <is>
-          <t>question</t>
+          <t>aspiration</t>
         </is>
       </c>
       <c r="J250" t="n">
@@ -27292,12 +27324,12 @@
       </c>
       <c r="K250" t="inlineStr">
         <is>
-          <t>curiosity_or_help_request</t>
+          <t>hope_or_urgent_public_request</t>
         </is>
       </c>
       <c r="L250" t="inlineStr">
         <is>
-          <t>question_or_information_seeking</t>
+          <t>public_expectation_or_action_request</t>
         </is>
       </c>
       <c r="M250" t="inlineStr">
@@ -27307,10 +27339,14 @@
       </c>
       <c r="N250" t="inlineStr">
         <is>
-          <t>Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Pertanyaan publik</t>
-        </is>
-      </c>
-      <c r="O250" t="inlineStr"/>
+          <t>Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Aspirasi &amp; permintaan tindak lanjut; Pertanyaan teknis publik</t>
+        </is>
+      </c>
+      <c r="O250" t="inlineStr">
+        <is>
+          <t>public_aspiration_needs_response</t>
+        </is>
+      </c>
       <c r="P250" t="b">
         <v>0</v>
       </c>
@@ -27386,7 +27422,7 @@
       </c>
       <c r="I251" t="inlineStr">
         <is>
-          <t>question</t>
+          <t>aspiration</t>
         </is>
       </c>
       <c r="J251" t="n">
@@ -27394,12 +27430,12 @@
       </c>
       <c r="K251" t="inlineStr">
         <is>
-          <t>curiosity_or_help_request</t>
+          <t>hope_or_urgent_public_request</t>
         </is>
       </c>
       <c r="L251" t="inlineStr">
         <is>
-          <t>question_or_information_seeking</t>
+          <t>public_expectation_or_action_request</t>
         </is>
       </c>
       <c r="M251" t="inlineStr">
@@ -27409,10 +27445,14 @@
       </c>
       <c r="N251" t="inlineStr">
         <is>
-          <t>Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Pertanyaan publik</t>
-        </is>
-      </c>
-      <c r="O251" t="inlineStr"/>
+          <t>Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Aspirasi &amp; permintaan tindak lanjut; Pertanyaan teknis publik</t>
+        </is>
+      </c>
+      <c r="O251" t="inlineStr">
+        <is>
+          <t>public_aspiration_needs_response</t>
+        </is>
+      </c>
       <c r="P251" t="b">
         <v>0</v>
       </c>
@@ -27511,7 +27551,7 @@
       </c>
       <c r="N252" t="inlineStr">
         <is>
-          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Pertanyaan publik</t>
+          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Aspirasi &amp; permintaan tindak lanjut; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O252" t="inlineStr"/>
@@ -27598,12 +27638,12 @@
       </c>
       <c r="K253" t="inlineStr">
         <is>
-          <t>curiosity_or_help_request</t>
+          <t>curiosity</t>
         </is>
       </c>
       <c r="L253" t="inlineStr">
         <is>
-          <t>question_or_information_seeking</t>
+          <t>technical_question_or_information_seeking</t>
         </is>
       </c>
       <c r="M253" t="inlineStr">
@@ -27613,7 +27653,7 @@
       </c>
       <c r="N253" t="inlineStr">
         <is>
-          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Pertanyaan publik</t>
+          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Aspirasi &amp; permintaan tindak lanjut; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O253" t="inlineStr">
@@ -27717,7 +27757,7 @@
       </c>
       <c r="N254" t="inlineStr">
         <is>
-          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Pertanyaan publik</t>
+          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Aspirasi &amp; permintaan tindak lanjut; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O254" t="inlineStr"/>
@@ -27817,7 +27857,7 @@
       </c>
       <c r="N255" t="inlineStr">
         <is>
-          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Dukungan &amp; apresiasi; Pertanyaan publik</t>
+          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Dukungan &amp; apresiasi; Aspirasi &amp; permintaan tindak lanjut; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O255" t="inlineStr"/>
@@ -27917,7 +27957,7 @@
       </c>
       <c r="N256" t="inlineStr">
         <is>
-          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Pertanyaan publik</t>
+          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Aspirasi &amp; permintaan tindak lanjut; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O256" t="inlineStr"/>
@@ -28017,7 +28057,7 @@
       </c>
       <c r="N257" t="inlineStr">
         <is>
-          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Pertanyaan publik</t>
+          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Aspirasi &amp; permintaan tindak lanjut; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O257" t="inlineStr"/>
@@ -28117,7 +28157,7 @@
       </c>
       <c r="N258" t="inlineStr">
         <is>
-          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Pertanyaan publik</t>
+          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Aspirasi &amp; permintaan tindak lanjut; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O258" t="inlineStr">
@@ -28221,7 +28261,7 @@
       </c>
       <c r="N259" t="inlineStr">
         <is>
-          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Pertanyaan publik</t>
+          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Aspirasi &amp; permintaan tindak lanjut; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O259" t="inlineStr"/>
@@ -28321,7 +28361,7 @@
       </c>
       <c r="N260" t="inlineStr">
         <is>
-          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Pertanyaan publik</t>
+          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Aspirasi &amp; permintaan tindak lanjut; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O260" t="inlineStr"/>
@@ -28398,7 +28438,7 @@
       </c>
       <c r="I261" t="inlineStr">
         <is>
-          <t>question</t>
+          <t>aspiration</t>
         </is>
       </c>
       <c r="J261" t="n">
@@ -28406,12 +28446,12 @@
       </c>
       <c r="K261" t="inlineStr">
         <is>
-          <t>curiosity_or_help_request</t>
+          <t>hope_or_urgent_public_request</t>
         </is>
       </c>
       <c r="L261" t="inlineStr">
         <is>
-          <t>question_or_information_seeking</t>
+          <t>public_expectation_or_action_request</t>
         </is>
       </c>
       <c r="M261" t="inlineStr">
@@ -28421,10 +28461,14 @@
       </c>
       <c r="N261" t="inlineStr">
         <is>
-          <t>Edukasi FOLU Net Sink 2030; Pertanyaan publik</t>
-        </is>
-      </c>
-      <c r="O261" t="inlineStr"/>
+          <t>Edukasi FOLU Net Sink 2030; Aspirasi &amp; permintaan tindak lanjut; Pertanyaan teknis publik</t>
+        </is>
+      </c>
+      <c r="O261" t="inlineStr">
+        <is>
+          <t>public_aspiration_needs_response</t>
+        </is>
+      </c>
       <c r="P261" t="b">
         <v>0</v>
       </c>
@@ -28500,7 +28544,7 @@
       </c>
       <c r="I262" t="inlineStr">
         <is>
-          <t>question</t>
+          <t>aspiration</t>
         </is>
       </c>
       <c r="J262" t="n">
@@ -28508,12 +28552,12 @@
       </c>
       <c r="K262" t="inlineStr">
         <is>
-          <t>curiosity_or_help_request</t>
+          <t>hope_or_urgent_public_request</t>
         </is>
       </c>
       <c r="L262" t="inlineStr">
         <is>
-          <t>question_or_information_seeking</t>
+          <t>public_expectation_or_action_request</t>
         </is>
       </c>
       <c r="M262" t="inlineStr">
@@ -28523,10 +28567,14 @@
       </c>
       <c r="N262" t="inlineStr">
         <is>
-          <t>Edukasi FOLU Net Sink 2030; Pertanyaan publik</t>
-        </is>
-      </c>
-      <c r="O262" t="inlineStr"/>
+          <t>Edukasi FOLU Net Sink 2030; Aspirasi &amp; permintaan tindak lanjut; Pertanyaan teknis publik</t>
+        </is>
+      </c>
+      <c r="O262" t="inlineStr">
+        <is>
+          <t>public_aspiration_needs_response</t>
+        </is>
+      </c>
       <c r="P262" t="b">
         <v>0</v>
       </c>
@@ -28623,7 +28671,7 @@
       </c>
       <c r="N263" t="inlineStr">
         <is>
-          <t>Edukasi FOLU Net Sink 2030; Pertanyaan publik</t>
+          <t>Edukasi FOLU Net Sink 2030; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O263" t="inlineStr"/>
@@ -28723,7 +28771,7 @@
       </c>
       <c r="N264" t="inlineStr">
         <is>
-          <t>Edukasi FOLU Net Sink 2030; Pertanyaan publik</t>
+          <t>Edukasi FOLU Net Sink 2030; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O264" t="inlineStr"/>
@@ -28823,7 +28871,7 @@
       </c>
       <c r="N265" t="inlineStr">
         <is>
-          <t>Edukasi FOLU Net Sink 2030; Pertanyaan publik</t>
+          <t>Edukasi FOLU Net Sink 2030; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O265" t="inlineStr"/>
@@ -28900,7 +28948,7 @@
       </c>
       <c r="I266" t="inlineStr">
         <is>
-          <t>negative</t>
+          <t>aspiration</t>
         </is>
       </c>
       <c r="J266" t="n">
@@ -28908,12 +28956,12 @@
       </c>
       <c r="K266" t="inlineStr">
         <is>
-          <t>concern</t>
+          <t>hope_or_urgent_public_request</t>
         </is>
       </c>
       <c r="L266" t="inlineStr">
         <is>
-          <t>critical_or_concern</t>
+          <t>public_expectation_or_action_request</t>
         </is>
       </c>
       <c r="M266" t="inlineStr">
@@ -28923,12 +28971,12 @@
       </c>
       <c r="N266" t="inlineStr">
         <is>
-          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Program lapangan &amp; daerah; Pertanyaan publik</t>
+          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Program lapangan &amp; daerah; Aspirasi &amp; permintaan tindak lanjut; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O266" t="inlineStr">
         <is>
-          <t>deforestation_criticism; unanswered_question</t>
+          <t>deforestation_criticism; public_aspiration_needs_response; unanswered_question</t>
         </is>
       </c>
       <c r="P266" t="b">
@@ -28959,7 +29007,7 @@
       </c>
       <c r="X266" t="inlineStr">
         <is>
-          <t>negative</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -29027,7 +29075,7 @@
       </c>
       <c r="N267" t="inlineStr">
         <is>
-          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Program lapangan &amp; daerah; Pertanyaan publik</t>
+          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Program lapangan &amp; daerah; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O267" t="inlineStr">
@@ -29110,7 +29158,7 @@
       </c>
       <c r="I268" t="inlineStr">
         <is>
-          <t>question</t>
+          <t>aspiration</t>
         </is>
       </c>
       <c r="J268" t="n">
@@ -29118,12 +29166,12 @@
       </c>
       <c r="K268" t="inlineStr">
         <is>
-          <t>curiosity_or_help_request</t>
+          <t>hope_or_urgent_public_request</t>
         </is>
       </c>
       <c r="L268" t="inlineStr">
         <is>
-          <t>question_or_information_seeking</t>
+          <t>public_expectation_or_action_request</t>
         </is>
       </c>
       <c r="M268" t="inlineStr">
@@ -29133,12 +29181,12 @@
       </c>
       <c r="N268" t="inlineStr">
         <is>
-          <t>Edukasi FOLU Net Sink 2030; Pertanyaan publik</t>
+          <t>Edukasi FOLU Net Sink 2030; Aspirasi &amp; permintaan tindak lanjut; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O268" t="inlineStr">
         <is>
-          <t>unanswered_question</t>
+          <t>public_aspiration_needs_response; unanswered_question</t>
         </is>
       </c>
       <c r="P268" t="b">
@@ -29239,7 +29287,7 @@
       </c>
       <c r="N269" t="inlineStr">
         <is>
-          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Program lapangan &amp; daerah; Pertanyaan publik</t>
+          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Program lapangan &amp; daerah; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O269" t="inlineStr">
@@ -29343,7 +29391,7 @@
       </c>
       <c r="N270" t="inlineStr">
         <is>
-          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Perhutanan sosial &amp; ekonomi karbon; Program lapangan &amp; daerah; Dukungan &amp; apresiasi; Pertanyaan publik</t>
+          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Perhutanan sosial &amp; ekonomi karbon; Program lapangan &amp; daerah; Dukungan &amp; apresiasi; Aspirasi &amp; permintaan tindak lanjut; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O270" t="inlineStr"/>
@@ -29443,7 +29491,7 @@
       </c>
       <c r="N271" t="inlineStr">
         <is>
-          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Perhutanan sosial &amp; ekonomi karbon; Program lapangan &amp; daerah; Dukungan &amp; apresiasi; Pertanyaan publik</t>
+          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Perhutanan sosial &amp; ekonomi karbon; Program lapangan &amp; daerah; Dukungan &amp; apresiasi; Aspirasi &amp; permintaan tindak lanjut; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O271" t="inlineStr"/>
@@ -29543,7 +29591,7 @@
       </c>
       <c r="N272" t="inlineStr">
         <is>
-          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Perhutanan sosial &amp; ekonomi karbon; Program lapangan &amp; daerah; Dukungan &amp; apresiasi; Pertanyaan publik</t>
+          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Perhutanan sosial &amp; ekonomi karbon; Program lapangan &amp; daerah; Dukungan &amp; apresiasi; Aspirasi &amp; permintaan tindak lanjut; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O272" t="inlineStr"/>
@@ -29628,12 +29676,12 @@
       </c>
       <c r="K273" t="inlineStr">
         <is>
-          <t>curiosity_or_help_request</t>
+          <t>curiosity</t>
         </is>
       </c>
       <c r="L273" t="inlineStr">
         <is>
-          <t>question_or_information_seeking</t>
+          <t>technical_question_or_information_seeking</t>
         </is>
       </c>
       <c r="M273" t="inlineStr">
@@ -29643,7 +29691,7 @@
       </c>
       <c r="N273" t="inlineStr">
         <is>
-          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Perhutanan sosial &amp; ekonomi karbon; Program lapangan &amp; daerah; Dukungan &amp; apresiasi; Pertanyaan publik</t>
+          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Perhutanan sosial &amp; ekonomi karbon; Program lapangan &amp; daerah; Dukungan &amp; apresiasi; Aspirasi &amp; permintaan tindak lanjut; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O273" t="inlineStr">
@@ -29734,12 +29782,12 @@
       </c>
       <c r="K274" t="inlineStr">
         <is>
-          <t>curiosity_or_help_request</t>
+          <t>curiosity</t>
         </is>
       </c>
       <c r="L274" t="inlineStr">
         <is>
-          <t>question_or_information_seeking</t>
+          <t>technical_question_or_information_seeking</t>
         </is>
       </c>
       <c r="M274" t="inlineStr">
@@ -29749,7 +29797,7 @@
       </c>
       <c r="N274" t="inlineStr">
         <is>
-          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Perhutanan sosial &amp; ekonomi karbon; Program lapangan &amp; daerah; Dukungan &amp; apresiasi; Pertanyaan publik</t>
+          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Perhutanan sosial &amp; ekonomi karbon; Program lapangan &amp; daerah; Dukungan &amp; apresiasi; Aspirasi &amp; permintaan tindak lanjut; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O274" t="inlineStr">
@@ -29853,7 +29901,7 @@
       </c>
       <c r="N275" t="inlineStr">
         <is>
-          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Perhutanan sosial &amp; ekonomi karbon; Program lapangan &amp; daerah; Dukungan &amp; apresiasi; Pertanyaan publik</t>
+          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Perhutanan sosial &amp; ekonomi karbon; Program lapangan &amp; daerah; Dukungan &amp; apresiasi; Aspirasi &amp; permintaan tindak lanjut; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O275" t="inlineStr"/>
@@ -29953,7 +30001,7 @@
       </c>
       <c r="N276" t="inlineStr">
         <is>
-          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Perhutanan sosial &amp; ekonomi karbon; Program lapangan &amp; daerah; Dukungan &amp; apresiasi; Pertanyaan publik</t>
+          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Perhutanan sosial &amp; ekonomi karbon; Program lapangan &amp; daerah; Dukungan &amp; apresiasi; Aspirasi &amp; permintaan tindak lanjut; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O276" t="inlineStr"/>
@@ -30142,12 +30190,12 @@
       </c>
       <c r="K278" t="inlineStr">
         <is>
-          <t>curiosity_or_help_request</t>
+          <t>curiosity</t>
         </is>
       </c>
       <c r="L278" t="inlineStr">
         <is>
-          <t>question_or_information_seeking</t>
+          <t>technical_question_or_information_seeking</t>
         </is>
       </c>
       <c r="M278" t="inlineStr">
@@ -30157,7 +30205,7 @@
       </c>
       <c r="N278" t="inlineStr">
         <is>
-          <t>Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Pertanyaan publik</t>
+          <t>Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O278" t="inlineStr">
@@ -30240,7 +30288,7 @@
       </c>
       <c r="I279" t="inlineStr">
         <is>
-          <t>question</t>
+          <t>aspiration</t>
         </is>
       </c>
       <c r="J279" t="n">
@@ -30248,12 +30296,12 @@
       </c>
       <c r="K279" t="inlineStr">
         <is>
-          <t>curiosity_or_help_request</t>
+          <t>hope_or_urgent_public_request</t>
         </is>
       </c>
       <c r="L279" t="inlineStr">
         <is>
-          <t>question_or_information_seeking</t>
+          <t>public_expectation_or_action_request</t>
         </is>
       </c>
       <c r="M279" t="inlineStr">
@@ -30263,10 +30311,14 @@
       </c>
       <c r="N279" t="inlineStr">
         <is>
-          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi</t>
-        </is>
-      </c>
-      <c r="O279" t="inlineStr"/>
+          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Aspirasi &amp; permintaan tindak lanjut</t>
+        </is>
+      </c>
+      <c r="O279" t="inlineStr">
+        <is>
+          <t>public_aspiration_needs_response</t>
+        </is>
+      </c>
       <c r="P279" t="b">
         <v>0</v>
       </c>
@@ -30365,7 +30417,7 @@
       </c>
       <c r="N280" t="inlineStr">
         <is>
-          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Pertanyaan publik</t>
+          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O280" t="inlineStr">
@@ -30471,7 +30523,7 @@
       </c>
       <c r="N281" t="inlineStr">
         <is>
-          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Program lapangan &amp; daerah; Pertanyaan publik</t>
+          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Program lapangan &amp; daerah; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O281" t="inlineStr">
@@ -30562,12 +30614,12 @@
       </c>
       <c r="K282" t="inlineStr">
         <is>
-          <t>curiosity_or_help_request</t>
+          <t>curiosity</t>
         </is>
       </c>
       <c r="L282" t="inlineStr">
         <is>
-          <t>question_or_information_seeking</t>
+          <t>technical_question_or_information_seeking</t>
         </is>
       </c>
       <c r="M282" t="inlineStr">
@@ -30577,7 +30629,7 @@
       </c>
       <c r="N282" t="inlineStr">
         <is>
-          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Pertanyaan publik</t>
+          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O282" t="inlineStr">
@@ -30683,7 +30735,7 @@
       </c>
       <c r="N283" t="inlineStr">
         <is>
-          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Program lapangan &amp; daerah; Pertanyaan publik</t>
+          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Program lapangan &amp; daerah; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O283" t="inlineStr">
@@ -30772,12 +30824,12 @@
       </c>
       <c r="K284" t="inlineStr">
         <is>
-          <t>curiosity_or_help_request</t>
+          <t>curiosity</t>
         </is>
       </c>
       <c r="L284" t="inlineStr">
         <is>
-          <t>question_or_information_seeking</t>
+          <t>technical_question_or_information_seeking</t>
         </is>
       </c>
       <c r="M284" t="inlineStr">
@@ -30787,7 +30839,7 @@
       </c>
       <c r="N284" t="inlineStr">
         <is>
-          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Pertanyaan publik</t>
+          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O284" t="inlineStr">
@@ -30868,7 +30920,7 @@
       </c>
       <c r="I285" t="inlineStr">
         <is>
-          <t>negative</t>
+          <t>aspiration</t>
         </is>
       </c>
       <c r="J285" t="n">
@@ -30876,12 +30928,12 @@
       </c>
       <c r="K285" t="inlineStr">
         <is>
-          <t>concern</t>
+          <t>hope_or_urgent_public_request</t>
         </is>
       </c>
       <c r="L285" t="inlineStr">
         <is>
-          <t>critical_or_concern</t>
+          <t>public_expectation_or_action_request</t>
         </is>
       </c>
       <c r="M285" t="inlineStr">
@@ -30891,12 +30943,12 @@
       </c>
       <c r="N285" t="inlineStr">
         <is>
-          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Program lapangan &amp; daerah; Pertanyaan publik</t>
+          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Program lapangan &amp; daerah; Aspirasi &amp; permintaan tindak lanjut; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O285" t="inlineStr">
         <is>
-          <t>deforestation_criticism; unanswered_question</t>
+          <t>deforestation_criticism; public_aspiration_needs_response; unanswered_question</t>
         </is>
       </c>
       <c r="P285" t="b">
@@ -30927,7 +30979,7 @@
       </c>
       <c r="X285" t="inlineStr">
         <is>
-          <t>negative</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -30995,7 +31047,7 @@
       </c>
       <c r="N286" t="inlineStr">
         <is>
-          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Pertanyaan publik</t>
+          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O286" t="inlineStr">
@@ -31099,7 +31151,7 @@
       </c>
       <c r="N287" t="inlineStr">
         <is>
-          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Program lapangan &amp; daerah; Pertanyaan publik</t>
+          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Program lapangan &amp; daerah; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O287" t="inlineStr">
@@ -31180,7 +31232,7 @@
       </c>
       <c r="I288" t="inlineStr">
         <is>
-          <t>question</t>
+          <t>aspiration</t>
         </is>
       </c>
       <c r="J288" t="n">
@@ -31188,12 +31240,12 @@
       </c>
       <c r="K288" t="inlineStr">
         <is>
-          <t>curiosity_or_help_request</t>
+          <t>hope_or_urgent_public_request</t>
         </is>
       </c>
       <c r="L288" t="inlineStr">
         <is>
-          <t>question_or_information_seeking</t>
+          <t>public_expectation_or_action_request</t>
         </is>
       </c>
       <c r="M288" t="inlineStr">
@@ -31203,12 +31255,12 @@
       </c>
       <c r="N288" t="inlineStr">
         <is>
-          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Pertanyaan publik</t>
+          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Aspirasi &amp; permintaan tindak lanjut; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O288" t="inlineStr">
         <is>
-          <t>unanswered_question</t>
+          <t>public_aspiration_needs_response; unanswered_question</t>
         </is>
       </c>
       <c r="P288" t="b">
@@ -31307,7 +31359,7 @@
       </c>
       <c r="N289" t="inlineStr">
         <is>
-          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Pertanyaan publik</t>
+          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Aspirasi &amp; permintaan tindak lanjut; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O289" t="inlineStr"/>
@@ -31409,7 +31461,7 @@
       </c>
       <c r="N290" t="inlineStr">
         <is>
-          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Pertanyaan publik</t>
+          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Aspirasi &amp; permintaan tindak lanjut; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O290" t="inlineStr"/>
@@ -31509,7 +31561,7 @@
       </c>
       <c r="N291" t="inlineStr">
         <is>
-          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Pertanyaan publik</t>
+          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Aspirasi &amp; permintaan tindak lanjut; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O291" t="inlineStr"/>
@@ -31611,7 +31663,7 @@
       </c>
       <c r="N292" t="inlineStr">
         <is>
-          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Pertanyaan publik</t>
+          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Aspirasi &amp; permintaan tindak lanjut; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O292" t="inlineStr"/>
@@ -31713,7 +31765,7 @@
       </c>
       <c r="N293" t="inlineStr">
         <is>
-          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Program lapangan &amp; daerah; Pertanyaan publik</t>
+          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Program lapangan &amp; daerah; Aspirasi &amp; permintaan tindak lanjut; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O293" t="inlineStr">
@@ -31819,7 +31871,7 @@
       </c>
       <c r="N294" t="inlineStr">
         <is>
-          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Program lapangan &amp; daerah; Pertanyaan publik</t>
+          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Program lapangan &amp; daerah; Aspirasi &amp; permintaan tindak lanjut; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O294" t="inlineStr">
@@ -31923,7 +31975,7 @@
       </c>
       <c r="N295" t="inlineStr">
         <is>
-          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Pertanyaan publik</t>
+          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O295" t="inlineStr"/>
@@ -32023,7 +32075,7 @@
       </c>
       <c r="N296" t="inlineStr">
         <is>
-          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Dukungan &amp; apresiasi; Pertanyaan publik</t>
+          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Dukungan &amp; apresiasi; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O296" t="inlineStr"/>
@@ -32123,7 +32175,7 @@
       </c>
       <c r="N297" t="inlineStr">
         <is>
-          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Program lapangan &amp; daerah; Pertanyaan publik</t>
+          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Program lapangan &amp; daerah; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O297" t="inlineStr">
@@ -32204,7 +32256,7 @@
       </c>
       <c r="I298" t="inlineStr">
         <is>
-          <t>question</t>
+          <t>aspiration</t>
         </is>
       </c>
       <c r="J298" t="n">
@@ -32212,12 +32264,12 @@
       </c>
       <c r="K298" t="inlineStr">
         <is>
-          <t>curiosity_or_help_request</t>
+          <t>hope_or_urgent_public_request</t>
         </is>
       </c>
       <c r="L298" t="inlineStr">
         <is>
-          <t>question_or_information_seeking</t>
+          <t>public_expectation_or_action_request</t>
         </is>
       </c>
       <c r="M298" t="inlineStr">
@@ -32227,10 +32279,14 @@
       </c>
       <c r="N298" t="inlineStr">
         <is>
-          <t>Edukasi FOLU Net Sink 2030</t>
-        </is>
-      </c>
-      <c r="O298" t="inlineStr"/>
+          <t>Edukasi FOLU Net Sink 2030; Aspirasi &amp; permintaan tindak lanjut</t>
+        </is>
+      </c>
+      <c r="O298" t="inlineStr">
+        <is>
+          <t>public_aspiration_needs_response</t>
+        </is>
+      </c>
       <c r="P298" t="b">
         <v>0</v>
       </c>
@@ -32329,7 +32385,7 @@
       </c>
       <c r="N299" t="inlineStr">
         <is>
-          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Program lapangan &amp; daerah; Pertanyaan publik</t>
+          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Program lapangan &amp; daerah; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O299" t="inlineStr">
@@ -32433,7 +32489,7 @@
       </c>
       <c r="N300" t="inlineStr">
         <is>
-          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Pertanyaan publik</t>
+          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O300" t="inlineStr"/>
@@ -32533,7 +32589,7 @@
       </c>
       <c r="N301" t="inlineStr">
         <is>
-          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Pertanyaan publik</t>
+          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O301" t="inlineStr"/>
@@ -32633,7 +32689,7 @@
       </c>
       <c r="N302" t="inlineStr">
         <is>
-          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Pertanyaan publik</t>
+          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Aspirasi &amp; permintaan tindak lanjut; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O302" t="inlineStr">
@@ -32858,12 +32914,12 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>curiosity_or_help_request</t>
+          <t>curiosity</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>question_or_information_seeking</t>
+          <t>technical_question_or_information_seeking</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -32873,7 +32929,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perhutanan sosial &amp; ekonomi karbon; Pertanyaan publik</t>
+          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perhutanan sosial &amp; ekonomi karbon; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -32973,7 +33029,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Deforestasi &amp; tata kelola hutan; Dukungan &amp; apresiasi; Pertanyaan publik</t>
+          <t>Deforestasi &amp; tata kelola hutan; Dukungan &amp; apresiasi; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O3" t="inlineStr"/>
@@ -33069,7 +33125,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Deforestasi &amp; tata kelola hutan; Dukungan &amp; apresiasi; Pertanyaan publik</t>
+          <t>Deforestasi &amp; tata kelola hutan; Dukungan &amp; apresiasi; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O4" t="inlineStr"/>
@@ -33265,7 +33321,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Edukasi FOLU Net Sink 2030; Program lapangan &amp; daerah; Dukungan &amp; apresiasi; Pertanyaan publik</t>
+          <t>Edukasi FOLU Net Sink 2030; Program lapangan &amp; daerah; Dukungan &amp; apresiasi; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -33446,12 +33502,12 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>curiosity_or_help_request</t>
+          <t>curiosity</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>question_or_information_seeking</t>
+          <t>technical_question_or_information_seeking</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -33461,7 +33517,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perhutanan sosial &amp; ekonomi karbon; Program lapangan &amp; daerah; Pertanyaan publik</t>
+          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perhutanan sosial &amp; ekonomi karbon; Program lapangan &amp; daerah; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -33546,12 +33602,12 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>curiosity_or_help_request</t>
+          <t>curiosity</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>question_or_information_seeking</t>
+          <t>technical_question_or_information_seeking</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -33561,7 +33617,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perhutanan sosial &amp; ekonomi karbon; Pertanyaan publik</t>
+          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perhutanan sosial &amp; ekonomi karbon; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -33646,12 +33702,12 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>curiosity_or_help_request</t>
+          <t>curiosity</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>question_or_information_seeking</t>
+          <t>technical_question_or_information_seeking</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -33661,7 +33717,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Perubahan iklim &amp; emisi; Program lapangan &amp; daerah; Pertanyaan publik</t>
+          <t>Perubahan iklim &amp; emisi; Program lapangan &amp; daerah; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -33746,12 +33802,12 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>curiosity_or_help_request</t>
+          <t>curiosity</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>question_or_information_seeking</t>
+          <t>technical_question_or_information_seeking</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -33761,7 +33817,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Perubahan iklim &amp; emisi; Program lapangan &amp; daerah; Pertanyaan publik</t>
+          <t>Perubahan iklim &amp; emisi; Program lapangan &amp; daerah; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -34057,7 +34113,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Deforestasi &amp; tata kelola hutan; Pertanyaan publik</t>
+          <t>Deforestasi &amp; tata kelola hutan; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -34430,12 +34486,12 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>curiosity_or_help_request</t>
+          <t>curiosity</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>question_or_information_seeking</t>
+          <t>technical_question_or_information_seeking</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -34445,7 +34501,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Pertanyaan publik</t>
+          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -34722,12 +34778,12 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>curiosity_or_help_request</t>
+          <t>curiosity</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>question_or_information_seeking</t>
+          <t>technical_question_or_information_seeking</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -34737,7 +34793,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perhutanan sosial &amp; ekonomi karbon; Pertanyaan publik</t>
+          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perhutanan sosial &amp; ekonomi karbon; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -34832,12 +34888,12 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Pertanyaan publik</t>
+          <t>Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Pertanyaan publik</t>
+          <t>Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O22" t="inlineStr"/>
@@ -34928,12 +34984,12 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Pertanyaan publik</t>
+          <t>Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>Pertanyaan publik</t>
+          <t>Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O23" t="inlineStr"/>
@@ -35024,12 +35080,12 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Pertanyaan publik</t>
+          <t>Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>Pertanyaan publik</t>
+          <t>Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O24" t="inlineStr"/>
@@ -35110,22 +35166,22 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>curiosity_or_help_request</t>
+          <t>curiosity</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>question_or_information_seeking</t>
+          <t>technical_question_or_information_seeking</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Pertanyaan publik</t>
+          <t>Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>Pertanyaan publik</t>
+          <t>Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -35210,22 +35266,22 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>curiosity_or_help_request</t>
+          <t>curiosity</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>question_or_information_seeking</t>
+          <t>technical_question_or_information_seeking</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Pertanyaan publik</t>
+          <t>Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>Pertanyaan publik</t>
+          <t>Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -35310,12 +35366,12 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>curiosity_or_help_request</t>
+          <t>curiosity</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>question_or_information_seeking</t>
+          <t>technical_question_or_information_seeking</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -35325,7 +35381,7 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>Perhutanan sosial &amp; ekonomi karbon; Pertanyaan publik</t>
+          <t>Perhutanan sosial &amp; ekonomi karbon; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -35425,7 +35481,7 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>Deforestasi &amp; tata kelola hutan; Pertanyaan publik</t>
+          <t>Deforestasi &amp; tata kelola hutan; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O28" t="inlineStr"/>
@@ -35521,7 +35577,7 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>Edukasi FOLU Net Sink 2030; Pertanyaan publik</t>
+          <t>Edukasi FOLU Net Sink 2030; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O29" t="inlineStr"/>
@@ -35617,7 +35673,7 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>Edukasi FOLU Net Sink 2030; Pertanyaan publik</t>
+          <t>Edukasi FOLU Net Sink 2030; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O30" t="inlineStr"/>
@@ -36069,7 +36125,7 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Pertanyaan publik</t>
+          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O35" t="inlineStr"/>
@@ -36159,7 +36215,7 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Pertanyaan publik</t>
+          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O36" t="inlineStr"/>
@@ -36249,7 +36305,7 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Pertanyaan publik</t>
+          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O37" t="inlineStr"/>
@@ -36316,7 +36372,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>negative</t>
+          <t>aspiration</t>
         </is>
       </c>
       <c r="J38" t="n">
@@ -36324,12 +36380,12 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>concern</t>
+          <t>hope_or_urgent_public_request</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>critical_or_concern</t>
+          <t>public_expectation_or_action_request</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -36339,10 +36395,14 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Pertanyaan publik</t>
-        </is>
-      </c>
-      <c r="O38" t="inlineStr"/>
+          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Aspirasi &amp; permintaan tindak lanjut; Pertanyaan teknis publik</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>public_aspiration_needs_response</t>
+        </is>
+      </c>
       <c r="P38" t="b">
         <v>0</v>
       </c>
@@ -36365,7 +36425,7 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>negative</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -36414,12 +36474,12 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>curiosity_or_help_request</t>
+          <t>curiosity</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>question_or_information_seeking</t>
+          <t>technical_question_or_information_seeking</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -36429,7 +36489,7 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Pertanyaan publik</t>
+          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
@@ -36500,7 +36560,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>question</t>
         </is>
       </c>
       <c r="J40" t="n">
@@ -36508,12 +36568,12 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>curiosity</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>neutral_or_unclear</t>
+          <t>technical_question_or_information_seeking</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -36523,7 +36583,7 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Pertanyaan publik</t>
+          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
@@ -36602,12 +36662,12 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>curiosity_or_help_request</t>
+          <t>curiosity</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>question_or_information_seeking</t>
+          <t>technical_question_or_information_seeking</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -36617,7 +36677,7 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Pertanyaan publik</t>
+          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
@@ -36711,7 +36771,7 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Pertanyaan publik</t>
+          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O42" t="inlineStr"/>
@@ -37236,12 +37296,12 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>curiosity_or_help_request</t>
+          <t>curiosity</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>question_or_information_seeking</t>
+          <t>technical_question_or_information_seeking</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -37251,7 +37311,7 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>Edukasi FOLU Net Sink 2030; Perhutanan sosial &amp; ekonomi karbon; Pertanyaan publik</t>
+          <t>Edukasi FOLU Net Sink 2030; Perhutanan sosial &amp; ekonomi karbon; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
@@ -37345,7 +37405,7 @@
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>Edukasi FOLU Net Sink 2030; Pertanyaan publik</t>
+          <t>Edukasi FOLU Net Sink 2030; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
@@ -38058,12 +38118,12 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>curiosity_or_help_request</t>
+          <t>curiosity</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>question_or_information_seeking</t>
+          <t>technical_question_or_information_seeking</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
@@ -38073,7 +38133,7 @@
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Pertanyaan publik</t>
+          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
@@ -38144,7 +38204,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>question</t>
+          <t>aspiration</t>
         </is>
       </c>
       <c r="J58" t="n">
@@ -38152,12 +38212,12 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>curiosity_or_help_request</t>
+          <t>hope_or_urgent_public_request</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>question_or_information_seeking</t>
+          <t>public_expectation_or_action_request</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
@@ -38167,12 +38227,12 @@
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030</t>
+          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Aspirasi &amp; permintaan tindak lanjut</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>deforestation_criticism</t>
+          <t>deforestation_criticism; public_aspiration_needs_response</t>
         </is>
       </c>
       <c r="P58" t="b">
@@ -38246,12 +38306,12 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>curiosity_or_help_request</t>
+          <t>curiosity</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>question_or_information_seeking</t>
+          <t>technical_question_or_information_seeking</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
@@ -38261,7 +38321,7 @@
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>Edukasi FOLU Net Sink 2030; Pertanyaan publik</t>
+          <t>Edukasi FOLU Net Sink 2030; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
@@ -38520,12 +38580,12 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>curiosity_or_help_request</t>
+          <t>curiosity</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>question_or_information_seeking</t>
+          <t>technical_question_or_information_seeking</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
@@ -38535,7 +38595,7 @@
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Pertanyaan publik</t>
+          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
@@ -38974,12 +39034,12 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>curiosity_or_help_request</t>
+          <t>curiosity</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>question_or_information_seeking</t>
+          <t>technical_question_or_information_seeking</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
@@ -38989,7 +39049,7 @@
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Pertanyaan publik</t>
+          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
@@ -39083,7 +39143,7 @@
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>Edukasi FOLU Net Sink 2030; Pertanyaan publik</t>
+          <t>Edukasi FOLU Net Sink 2030; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O68" t="inlineStr"/>
@@ -39173,7 +39233,7 @@
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>Edukasi FOLU Net Sink 2030; Dukungan &amp; apresiasi; Pertanyaan publik</t>
+          <t>Edukasi FOLU Net Sink 2030; Dukungan &amp; apresiasi; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O69" t="inlineStr"/>
@@ -39240,7 +39300,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>question</t>
         </is>
       </c>
       <c r="J70" t="n">
@@ -39248,12 +39308,12 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>curiosity</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>neutral_or_unclear</t>
+          <t>technical_question_or_information_seeking</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -39263,7 +39323,7 @@
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>Edukasi FOLU Net Sink 2030; Pertanyaan publik</t>
+          <t>Edukasi FOLU Net Sink 2030; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
@@ -39334,7 +39394,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>question</t>
+          <t>aspiration</t>
         </is>
       </c>
       <c r="J71" t="n">
@@ -39342,12 +39402,12 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>curiosity_or_help_request</t>
+          <t>hope_or_urgent_public_request</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>question_or_information_seeking</t>
+          <t>public_expectation_or_action_request</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -39357,7 +39417,7 @@
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>Edukasi FOLU Net Sink 2030; Pertanyaan publik</t>
+          <t>Edukasi FOLU Net Sink 2030; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
@@ -39451,7 +39511,7 @@
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Pertanyaan publik</t>
+          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O72" t="inlineStr"/>
@@ -39984,7 +40044,7 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>question</t>
+          <t>aspiration</t>
         </is>
       </c>
       <c r="J78" t="n">
@@ -39992,12 +40052,12 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>curiosity_or_help_request</t>
+          <t>hope_or_urgent_public_request</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>question_or_information_seeking</t>
+          <t>public_expectation_or_action_request</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
@@ -40007,10 +40067,14 @@
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Program lapangan &amp; daerah</t>
-        </is>
-      </c>
-      <c r="O78" t="inlineStr"/>
+          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Program lapangan &amp; daerah; Aspirasi &amp; permintaan tindak lanjut</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>public_aspiration_needs_response</t>
+        </is>
+      </c>
       <c r="P78" t="b">
         <v>0</v>
       </c>
@@ -40094,12 +40158,12 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>curiosity_or_help_request</t>
+          <t>curiosity</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>question_or_information_seeking</t>
+          <t>technical_question_or_information_seeking</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
@@ -40200,12 +40264,12 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>curiosity_or_help_request</t>
+          <t>curiosity</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>question_or_information_seeking</t>
+          <t>technical_question_or_information_seeking</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
@@ -40215,7 +40279,7 @@
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Program lapangan &amp; daerah; Pertanyaan publik</t>
+          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Program lapangan &amp; daerah; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O80" t="inlineStr">
@@ -40408,12 +40472,12 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>curiosity_or_help_request</t>
+          <t>curiosity</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>question_or_information_seeking</t>
+          <t>technical_question_or_information_seeking</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
@@ -40423,7 +40487,7 @@
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Program lapangan &amp; daerah; Pertanyaan publik</t>
+          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Program lapangan &amp; daerah; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O82" t="inlineStr">
@@ -40822,12 +40886,12 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>curiosity_or_help_request</t>
+          <t>curiosity</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>question_or_information_seeking</t>
+          <t>technical_question_or_information_seeking</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
@@ -40837,7 +40901,7 @@
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Program lapangan &amp; daerah; Pertanyaan publik</t>
+          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Program lapangan &amp; daerah; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O86" t="inlineStr">
@@ -40943,7 +41007,7 @@
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Program lapangan &amp; daerah; Pertanyaan publik</t>
+          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Program lapangan &amp; daerah; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O87" t="inlineStr">
@@ -41253,7 +41317,7 @@
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perhutanan sosial &amp; ekonomi karbon; Program lapangan &amp; daerah; Pertanyaan publik</t>
+          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perhutanan sosial &amp; ekonomi karbon; Program lapangan &amp; daerah; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O90" t="inlineStr">
@@ -41538,7 +41602,7 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>question</t>
         </is>
       </c>
       <c r="J93" t="n">
@@ -41546,12 +41610,12 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>curiosity</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>neutral_or_unclear</t>
+          <t>technical_question_or_information_seeking</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
@@ -41561,7 +41625,7 @@
       </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Program lapangan &amp; daerah; Pertanyaan publik</t>
+          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Program lapangan &amp; daerah; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O93" t="inlineStr">
@@ -41652,12 +41716,12 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>curiosity_or_help_request</t>
+          <t>curiosity</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>question_or_information_seeking</t>
+          <t>technical_question_or_information_seeking</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
@@ -41667,7 +41731,7 @@
       </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Program lapangan &amp; daerah; Pertanyaan publik</t>
+          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Program lapangan &amp; daerah; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O94" t="inlineStr">
@@ -42466,7 +42530,7 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>positive</t>
+          <t>question</t>
         </is>
       </c>
       <c r="J102" t="n">
@@ -42474,12 +42538,12 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>appreciation</t>
+          <t>curiosity</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>supportive_or_appreciative</t>
+          <t>technical_question_or_information_seeking</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
@@ -42489,7 +42553,7 @@
       </c>
       <c r="N102" t="inlineStr">
         <is>
-          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Program lapangan &amp; daerah; Pertanyaan publik</t>
+          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Program lapangan &amp; daerah; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O102" t="inlineStr">
@@ -42527,7 +42591,7 @@
       </c>
       <c r="X102" t="inlineStr">
         <is>
-          <t>positive</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -42682,12 +42746,12 @@
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>curiosity_or_help_request</t>
+          <t>curiosity</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>question_or_information_seeking</t>
+          <t>technical_question_or_information_seeking</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
@@ -42697,7 +42761,7 @@
       </c>
       <c r="N104" t="inlineStr">
         <is>
-          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Program lapangan &amp; daerah; Pertanyaan publik</t>
+          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Program lapangan &amp; daerah; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O104" t="inlineStr">
@@ -43606,12 +43670,12 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>curiosity_or_help_request</t>
+          <t>curiosity</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>question_or_information_seeking</t>
+          <t>technical_question_or_information_seeking</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
@@ -43621,7 +43685,7 @@
       </c>
       <c r="N113" t="inlineStr">
         <is>
-          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Program lapangan &amp; daerah; Pertanyaan publik</t>
+          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Program lapangan &amp; daerah; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O113" t="inlineStr">
@@ -44310,7 +44374,7 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>question</t>
+          <t>aspiration</t>
         </is>
       </c>
       <c r="J120" t="n">
@@ -44318,12 +44382,12 @@
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>curiosity_or_help_request</t>
+          <t>hope_or_urgent_public_request</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>question_or_information_seeking</t>
+          <t>public_expectation_or_action_request</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
@@ -44333,10 +44397,14 @@
       </c>
       <c r="N120" t="inlineStr">
         <is>
-          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Program lapangan &amp; daerah</t>
-        </is>
-      </c>
-      <c r="O120" t="inlineStr"/>
+          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Program lapangan &amp; daerah; Aspirasi &amp; permintaan tindak lanjut</t>
+        </is>
+      </c>
+      <c r="O120" t="inlineStr">
+        <is>
+          <t>public_aspiration_needs_response</t>
+        </is>
+      </c>
       <c r="P120" t="b">
         <v>0</v>
       </c>
@@ -44520,12 +44588,12 @@
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>curiosity_or_help_request</t>
+          <t>curiosity</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>question_or_information_seeking</t>
+          <t>technical_question_or_information_seeking</t>
         </is>
       </c>
       <c r="M122" t="inlineStr">
@@ -44535,7 +44603,7 @@
       </c>
       <c r="N122" t="inlineStr">
         <is>
-          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Program lapangan &amp; daerah; Pertanyaan publik</t>
+          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Program lapangan &amp; daerah; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O122" t="inlineStr">
@@ -45026,12 +45094,12 @@
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>curiosity_or_help_request</t>
+          <t>curiosity</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>question_or_information_seeking</t>
+          <t>technical_question_or_information_seeking</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
@@ -45041,7 +45109,7 @@
       </c>
       <c r="N127" t="inlineStr">
         <is>
-          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Program lapangan &amp; daerah; Pertanyaan publik</t>
+          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Program lapangan &amp; daerah; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O127" t="inlineStr">
@@ -45245,7 +45313,7 @@
       </c>
       <c r="N129" t="inlineStr">
         <is>
-          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perhutanan sosial &amp; ekonomi karbon; Program lapangan &amp; daerah; Pertanyaan publik</t>
+          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perhutanan sosial &amp; ekonomi karbon; Program lapangan &amp; daerah; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O129" t="inlineStr">
@@ -45638,12 +45706,12 @@
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>curiosity_or_help_request</t>
+          <t>curiosity</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>question_or_information_seeking</t>
+          <t>technical_question_or_information_seeking</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
@@ -45653,7 +45721,7 @@
       </c>
       <c r="N133" t="inlineStr">
         <is>
-          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Program lapangan &amp; daerah; Pertanyaan publik</t>
+          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Program lapangan &amp; daerah; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O133" t="inlineStr">
@@ -45744,12 +45812,12 @@
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>curiosity_or_help_request</t>
+          <t>curiosity</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>question_or_information_seeking</t>
+          <t>technical_question_or_information_seeking</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
@@ -45759,7 +45827,7 @@
       </c>
       <c r="N134" t="inlineStr">
         <is>
-          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Program lapangan &amp; daerah; Pertanyaan publik</t>
+          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Program lapangan &amp; daerah; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O134" t="inlineStr">
@@ -46152,12 +46220,12 @@
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>curiosity_or_help_request</t>
+          <t>curiosity</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>question_or_information_seeking</t>
+          <t>technical_question_or_information_seeking</t>
         </is>
       </c>
       <c r="M138" t="inlineStr">
@@ -46167,7 +46235,7 @@
       </c>
       <c r="N138" t="inlineStr">
         <is>
-          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Program lapangan &amp; daerah; Pertanyaan publik</t>
+          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Program lapangan &amp; daerah; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O138" t="inlineStr">
@@ -46664,12 +46732,12 @@
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>curiosity_or_help_request</t>
+          <t>curiosity</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>question_or_information_seeking</t>
+          <t>technical_question_or_information_seeking</t>
         </is>
       </c>
       <c r="M143" t="inlineStr">
@@ -46679,7 +46747,7 @@
       </c>
       <c r="N143" t="inlineStr">
         <is>
-          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Program lapangan &amp; daerah; Pertanyaan publik</t>
+          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Program lapangan &amp; daerah; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O143" t="inlineStr">
@@ -46770,12 +46838,12 @@
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>curiosity_or_help_request</t>
+          <t>curiosity</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>question_or_information_seeking</t>
+          <t>technical_question_or_information_seeking</t>
         </is>
       </c>
       <c r="M144" t="inlineStr">
@@ -46785,7 +46853,7 @@
       </c>
       <c r="N144" t="inlineStr">
         <is>
-          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Program lapangan &amp; daerah; Pertanyaan publik</t>
+          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Program lapangan &amp; daerah; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O144" t="inlineStr">
@@ -46978,12 +47046,12 @@
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>curiosity_or_help_request</t>
+          <t>curiosity</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>question_or_information_seeking</t>
+          <t>technical_question_or_information_seeking</t>
         </is>
       </c>
       <c r="M146" t="inlineStr">
@@ -46993,7 +47061,7 @@
       </c>
       <c r="N146" t="inlineStr">
         <is>
-          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Program lapangan &amp; daerah; Pertanyaan publik</t>
+          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Program lapangan &amp; daerah; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O146" t="inlineStr">
@@ -47074,7 +47142,7 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>question</t>
         </is>
       </c>
       <c r="J147" t="n">
@@ -47082,12 +47150,12 @@
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>curiosity</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>neutral_or_unclear</t>
+          <t>technical_question_or_information_seeking</t>
         </is>
       </c>
       <c r="M147" t="inlineStr">
@@ -47097,7 +47165,7 @@
       </c>
       <c r="N147" t="inlineStr">
         <is>
-          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Program lapangan &amp; daerah; Pertanyaan publik</t>
+          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Program lapangan &amp; daerah; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O147" t="inlineStr">
@@ -47388,12 +47456,12 @@
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>curiosity_or_help_request</t>
+          <t>curiosity</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>question_or_information_seeking</t>
+          <t>technical_question_or_information_seeking</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
@@ -47403,7 +47471,7 @@
       </c>
       <c r="N150" t="inlineStr">
         <is>
-          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Program lapangan &amp; daerah; Pertanyaan publik</t>
+          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Program lapangan &amp; daerah; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O150" t="inlineStr">
@@ -47692,12 +47760,12 @@
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>curiosity_or_help_request</t>
+          <t>curiosity</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>question_or_information_seeking</t>
+          <t>technical_question_or_information_seeking</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
@@ -47707,7 +47775,7 @@
       </c>
       <c r="N153" t="inlineStr">
         <is>
-          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Program lapangan &amp; daerah; Pertanyaan publik</t>
+          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Program lapangan &amp; daerah; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O153" t="inlineStr">
@@ -48200,12 +48268,12 @@
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>curiosity_or_help_request</t>
+          <t>curiosity</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t>question_or_information_seeking</t>
+          <t>technical_question_or_information_seeking</t>
         </is>
       </c>
       <c r="M158" t="inlineStr">
@@ -48215,7 +48283,7 @@
       </c>
       <c r="N158" t="inlineStr">
         <is>
-          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Program lapangan &amp; daerah; Pertanyaan publik</t>
+          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Program lapangan &amp; daerah; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O158" t="inlineStr">
@@ -48396,7 +48464,7 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>aspiration</t>
         </is>
       </c>
       <c r="J160" t="n">
@@ -48404,12 +48472,12 @@
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>hope_or_urgent_public_request</t>
         </is>
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t>neutral_or_unclear</t>
+          <t>public_expectation_or_action_request</t>
         </is>
       </c>
       <c r="M160" t="inlineStr">
@@ -49198,7 +49266,7 @@
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>question</t>
+          <t>aspiration</t>
         </is>
       </c>
       <c r="J168" t="n">
@@ -49206,12 +49274,12 @@
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t>curiosity_or_help_request</t>
+          <t>hope_or_urgent_public_request</t>
         </is>
       </c>
       <c r="L168" t="inlineStr">
         <is>
-          <t>question_or_information_seeking</t>
+          <t>public_expectation_or_action_request</t>
         </is>
       </c>
       <c r="M168" t="inlineStr">
@@ -49221,10 +49289,14 @@
       </c>
       <c r="N168" t="inlineStr">
         <is>
-          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Program lapangan &amp; daerah</t>
-        </is>
-      </c>
-      <c r="O168" t="inlineStr"/>
+          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Program lapangan &amp; daerah; Aspirasi &amp; permintaan tindak lanjut</t>
+        </is>
+      </c>
+      <c r="O168" t="inlineStr">
+        <is>
+          <t>public_aspiration_needs_response</t>
+        </is>
+      </c>
       <c r="P168" t="b">
         <v>0</v>
       </c>
@@ -49306,12 +49378,12 @@
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t>curiosity_or_help_request</t>
+          <t>curiosity</t>
         </is>
       </c>
       <c r="L169" t="inlineStr">
         <is>
-          <t>question_or_information_seeking</t>
+          <t>technical_question_or_information_seeking</t>
         </is>
       </c>
       <c r="M169" t="inlineStr">
@@ -49321,7 +49393,7 @@
       </c>
       <c r="N169" t="inlineStr">
         <is>
-          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Program lapangan &amp; daerah; Pertanyaan publik</t>
+          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Program lapangan &amp; daerah; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O169" t="inlineStr">
@@ -50227,7 +50299,7 @@
       </c>
       <c r="N178" t="inlineStr">
         <is>
-          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Program lapangan &amp; daerah; Pertanyaan publik</t>
+          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Program lapangan &amp; daerah; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O178" t="inlineStr">
@@ -50318,12 +50390,12 @@
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t>curiosity_or_help_request</t>
+          <t>curiosity</t>
         </is>
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t>question_or_information_seeking</t>
+          <t>technical_question_or_information_seeking</t>
         </is>
       </c>
       <c r="M179" t="inlineStr">
@@ -50524,12 +50596,12 @@
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t>curiosity_or_help_request</t>
+          <t>curiosity</t>
         </is>
       </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t>question_or_information_seeking</t>
+          <t>technical_question_or_information_seeking</t>
         </is>
       </c>
       <c r="M181" t="inlineStr">
@@ -50539,7 +50611,7 @@
       </c>
       <c r="N181" t="inlineStr">
         <is>
-          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Program lapangan &amp; daerah; Pertanyaan publik</t>
+          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Program lapangan &amp; daerah; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O181" t="inlineStr">
@@ -50628,12 +50700,12 @@
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t>curiosity_or_help_request</t>
+          <t>curiosity</t>
         </is>
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t>question_or_information_seeking</t>
+          <t>technical_question_or_information_seeking</t>
         </is>
       </c>
       <c r="M182" t="inlineStr">
@@ -50643,7 +50715,7 @@
       </c>
       <c r="N182" t="inlineStr">
         <is>
-          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Program lapangan &amp; daerah; Pertanyaan publik</t>
+          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Program lapangan &amp; daerah; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O182" t="inlineStr">
@@ -50732,12 +50804,12 @@
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t>curiosity_or_help_request</t>
+          <t>curiosity</t>
         </is>
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t>question_or_information_seeking</t>
+          <t>technical_question_or_information_seeking</t>
         </is>
       </c>
       <c r="M183" t="inlineStr">
@@ -50747,7 +50819,7 @@
       </c>
       <c r="N183" t="inlineStr">
         <is>
-          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Program lapangan &amp; daerah; Pertanyaan publik</t>
+          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Program lapangan &amp; daerah; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O183" t="inlineStr">
@@ -50928,7 +51000,7 @@
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>question</t>
+          <t>aspiration</t>
         </is>
       </c>
       <c r="J185" t="n">
@@ -50936,12 +51008,12 @@
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t>curiosity_or_help_request</t>
+          <t>hope_or_urgent_public_request</t>
         </is>
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>question_or_information_seeking</t>
+          <t>public_expectation_or_action_request</t>
         </is>
       </c>
       <c r="M185" t="inlineStr">
@@ -50951,10 +51023,14 @@
       </c>
       <c r="N185" t="inlineStr">
         <is>
-          <t>Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Pertanyaan publik</t>
-        </is>
-      </c>
-      <c r="O185" t="inlineStr"/>
+          <t>Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Aspirasi &amp; permintaan tindak lanjut; Pertanyaan teknis publik</t>
+        </is>
+      </c>
+      <c r="O185" t="inlineStr">
+        <is>
+          <t>public_aspiration_needs_response</t>
+        </is>
+      </c>
       <c r="P185" t="b">
         <v>0</v>
       </c>
@@ -51053,7 +51129,7 @@
       </c>
       <c r="N186" t="inlineStr">
         <is>
-          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Pertanyaan publik</t>
+          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O186" t="inlineStr"/>
@@ -51132,7 +51208,7 @@
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>question</t>
+          <t>aspiration</t>
         </is>
       </c>
       <c r="J187" t="n">
@@ -51140,12 +51216,12 @@
       </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t>curiosity_or_help_request</t>
+          <t>hope_or_urgent_public_request</t>
         </is>
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t>question_or_information_seeking</t>
+          <t>public_expectation_or_action_request</t>
         </is>
       </c>
       <c r="M187" t="inlineStr">
@@ -51155,10 +51231,14 @@
       </c>
       <c r="N187" t="inlineStr">
         <is>
-          <t>Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Pertanyaan publik</t>
-        </is>
-      </c>
-      <c r="O187" t="inlineStr"/>
+          <t>Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Aspirasi &amp; permintaan tindak lanjut; Pertanyaan teknis publik</t>
+        </is>
+      </c>
+      <c r="O187" t="inlineStr">
+        <is>
+          <t>public_aspiration_needs_response</t>
+        </is>
+      </c>
       <c r="P187" t="b">
         <v>0</v>
       </c>
@@ -51255,7 +51335,7 @@
       </c>
       <c r="N188" t="inlineStr">
         <is>
-          <t>Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Pertanyaan publik</t>
+          <t>Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O188" t="inlineStr"/>
@@ -51334,7 +51414,7 @@
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>question</t>
+          <t>aspiration</t>
         </is>
       </c>
       <c r="J189" t="n">
@@ -51342,12 +51422,12 @@
       </c>
       <c r="K189" t="inlineStr">
         <is>
-          <t>curiosity_or_help_request</t>
+          <t>hope_or_urgent_public_request</t>
         </is>
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t>question_or_information_seeking</t>
+          <t>public_expectation_or_action_request</t>
         </is>
       </c>
       <c r="M189" t="inlineStr">
@@ -51357,10 +51437,14 @@
       </c>
       <c r="N189" t="inlineStr">
         <is>
-          <t>Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Pertanyaan publik</t>
-        </is>
-      </c>
-      <c r="O189" t="inlineStr"/>
+          <t>Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Aspirasi &amp; permintaan tindak lanjut; Pertanyaan teknis publik</t>
+        </is>
+      </c>
+      <c r="O189" t="inlineStr">
+        <is>
+          <t>public_aspiration_needs_response</t>
+        </is>
+      </c>
       <c r="P189" t="b">
         <v>0</v>
       </c>
@@ -51444,12 +51528,12 @@
       </c>
       <c r="K190" t="inlineStr">
         <is>
-          <t>curiosity_or_help_request</t>
+          <t>curiosity</t>
         </is>
       </c>
       <c r="L190" t="inlineStr">
         <is>
-          <t>question_or_information_seeking</t>
+          <t>technical_question_or_information_seeking</t>
         </is>
       </c>
       <c r="M190" t="inlineStr">
@@ -51459,7 +51543,7 @@
       </c>
       <c r="N190" t="inlineStr">
         <is>
-          <t>Konflik lahan &amp; hutan lindung; Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Pertanyaan publik</t>
+          <t>Konflik lahan &amp; hutan lindung; Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O190" t="inlineStr">
@@ -51563,7 +51647,7 @@
       </c>
       <c r="N191" t="inlineStr">
         <is>
-          <t>Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Pertanyaan publik</t>
+          <t>Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O191" t="inlineStr"/>
@@ -51665,7 +51749,7 @@
       </c>
       <c r="N192" t="inlineStr">
         <is>
-          <t>Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Pertanyaan publik</t>
+          <t>Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O192" t="inlineStr">
@@ -51754,12 +51838,12 @@
       </c>
       <c r="K193" t="inlineStr">
         <is>
-          <t>curiosity_or_help_request</t>
+          <t>curiosity</t>
         </is>
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>question_or_information_seeking</t>
+          <t>technical_question_or_information_seeking</t>
         </is>
       </c>
       <c r="M193" t="inlineStr">
@@ -51769,7 +51853,7 @@
       </c>
       <c r="N193" t="inlineStr">
         <is>
-          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Pertanyaan publik</t>
+          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O193" t="inlineStr">
@@ -51852,7 +51936,7 @@
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>question</t>
+          <t>aspiration</t>
         </is>
       </c>
       <c r="J194" t="n">
@@ -51860,12 +51944,12 @@
       </c>
       <c r="K194" t="inlineStr">
         <is>
-          <t>curiosity_or_help_request</t>
+          <t>hope_or_urgent_public_request</t>
         </is>
       </c>
       <c r="L194" t="inlineStr">
         <is>
-          <t>question_or_information_seeking</t>
+          <t>public_expectation_or_action_request</t>
         </is>
       </c>
       <c r="M194" t="inlineStr">
@@ -51875,10 +51959,14 @@
       </c>
       <c r="N194" t="inlineStr">
         <is>
-          <t>Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Pertanyaan publik</t>
-        </is>
-      </c>
-      <c r="O194" t="inlineStr"/>
+          <t>Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Aspirasi &amp; permintaan tindak lanjut; Pertanyaan teknis publik</t>
+        </is>
+      </c>
+      <c r="O194" t="inlineStr">
+        <is>
+          <t>public_aspiration_needs_response</t>
+        </is>
+      </c>
       <c r="P194" t="b">
         <v>0</v>
       </c>
@@ -51954,7 +52042,7 @@
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>question</t>
+          <t>aspiration</t>
         </is>
       </c>
       <c r="J195" t="n">
@@ -51962,12 +52050,12 @@
       </c>
       <c r="K195" t="inlineStr">
         <is>
-          <t>curiosity_or_help_request</t>
+          <t>hope_or_urgent_public_request</t>
         </is>
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t>question_or_information_seeking</t>
+          <t>public_expectation_or_action_request</t>
         </is>
       </c>
       <c r="M195" t="inlineStr">
@@ -51977,10 +52065,14 @@
       </c>
       <c r="N195" t="inlineStr">
         <is>
-          <t>Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Pertanyaan publik</t>
-        </is>
-      </c>
-      <c r="O195" t="inlineStr"/>
+          <t>Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Aspirasi &amp; permintaan tindak lanjut; Pertanyaan teknis publik</t>
+        </is>
+      </c>
+      <c r="O195" t="inlineStr">
+        <is>
+          <t>public_aspiration_needs_response</t>
+        </is>
+      </c>
       <c r="P195" t="b">
         <v>0</v>
       </c>
@@ -52056,7 +52148,7 @@
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>question</t>
+          <t>aspiration</t>
         </is>
       </c>
       <c r="J196" t="n">
@@ -52064,12 +52156,12 @@
       </c>
       <c r="K196" t="inlineStr">
         <is>
-          <t>curiosity_or_help_request</t>
+          <t>hope_or_urgent_public_request</t>
         </is>
       </c>
       <c r="L196" t="inlineStr">
         <is>
-          <t>question_or_information_seeking</t>
+          <t>public_expectation_or_action_request</t>
         </is>
       </c>
       <c r="M196" t="inlineStr">
@@ -52079,10 +52171,14 @@
       </c>
       <c r="N196" t="inlineStr">
         <is>
-          <t>Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Pertanyaan publik</t>
-        </is>
-      </c>
-      <c r="O196" t="inlineStr"/>
+          <t>Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Aspirasi &amp; permintaan tindak lanjut; Pertanyaan teknis publik</t>
+        </is>
+      </c>
+      <c r="O196" t="inlineStr">
+        <is>
+          <t>public_aspiration_needs_response</t>
+        </is>
+      </c>
       <c r="P196" t="b">
         <v>0</v>
       </c>
@@ -52181,7 +52277,7 @@
       </c>
       <c r="N197" t="inlineStr">
         <is>
-          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Pertanyaan publik</t>
+          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Aspirasi &amp; permintaan tindak lanjut; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O197" t="inlineStr"/>
@@ -52268,12 +52364,12 @@
       </c>
       <c r="K198" t="inlineStr">
         <is>
-          <t>curiosity_or_help_request</t>
+          <t>curiosity</t>
         </is>
       </c>
       <c r="L198" t="inlineStr">
         <is>
-          <t>question_or_information_seeking</t>
+          <t>technical_question_or_information_seeking</t>
         </is>
       </c>
       <c r="M198" t="inlineStr">
@@ -52283,7 +52379,7 @@
       </c>
       <c r="N198" t="inlineStr">
         <is>
-          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Pertanyaan publik</t>
+          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Aspirasi &amp; permintaan tindak lanjut; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O198" t="inlineStr">
@@ -52387,7 +52483,7 @@
       </c>
       <c r="N199" t="inlineStr">
         <is>
-          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Dukungan &amp; apresiasi; Pertanyaan publik</t>
+          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Dukungan &amp; apresiasi; Aspirasi &amp; permintaan tindak lanjut; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O199" t="inlineStr"/>
@@ -52487,7 +52583,7 @@
       </c>
       <c r="N200" t="inlineStr">
         <is>
-          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Pertanyaan publik</t>
+          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Aspirasi &amp; permintaan tindak lanjut; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O200" t="inlineStr">
@@ -52568,7 +52664,7 @@
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>question</t>
+          <t>aspiration</t>
         </is>
       </c>
       <c r="J201" t="n">
@@ -52576,12 +52672,12 @@
       </c>
       <c r="K201" t="inlineStr">
         <is>
-          <t>curiosity_or_help_request</t>
+          <t>hope_or_urgent_public_request</t>
         </is>
       </c>
       <c r="L201" t="inlineStr">
         <is>
-          <t>question_or_information_seeking</t>
+          <t>public_expectation_or_action_request</t>
         </is>
       </c>
       <c r="M201" t="inlineStr">
@@ -52591,10 +52687,14 @@
       </c>
       <c r="N201" t="inlineStr">
         <is>
-          <t>Edukasi FOLU Net Sink 2030; Pertanyaan publik</t>
-        </is>
-      </c>
-      <c r="O201" t="inlineStr"/>
+          <t>Edukasi FOLU Net Sink 2030; Aspirasi &amp; permintaan tindak lanjut; Pertanyaan teknis publik</t>
+        </is>
+      </c>
+      <c r="O201" t="inlineStr">
+        <is>
+          <t>public_aspiration_needs_response</t>
+        </is>
+      </c>
       <c r="P201" t="b">
         <v>0</v>
       </c>
@@ -52670,7 +52770,7 @@
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>question</t>
+          <t>aspiration</t>
         </is>
       </c>
       <c r="J202" t="n">
@@ -52678,12 +52778,12 @@
       </c>
       <c r="K202" t="inlineStr">
         <is>
-          <t>curiosity_or_help_request</t>
+          <t>hope_or_urgent_public_request</t>
         </is>
       </c>
       <c r="L202" t="inlineStr">
         <is>
-          <t>question_or_information_seeking</t>
+          <t>public_expectation_or_action_request</t>
         </is>
       </c>
       <c r="M202" t="inlineStr">
@@ -52693,10 +52793,14 @@
       </c>
       <c r="N202" t="inlineStr">
         <is>
-          <t>Edukasi FOLU Net Sink 2030; Pertanyaan publik</t>
-        </is>
-      </c>
-      <c r="O202" t="inlineStr"/>
+          <t>Edukasi FOLU Net Sink 2030; Aspirasi &amp; permintaan tindak lanjut; Pertanyaan teknis publik</t>
+        </is>
+      </c>
+      <c r="O202" t="inlineStr">
+        <is>
+          <t>public_aspiration_needs_response</t>
+        </is>
+      </c>
       <c r="P202" t="b">
         <v>0</v>
       </c>
@@ -52793,7 +52897,7 @@
       </c>
       <c r="N203" t="inlineStr">
         <is>
-          <t>Edukasi FOLU Net Sink 2030; Pertanyaan publik</t>
+          <t>Edukasi FOLU Net Sink 2030; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O203" t="inlineStr"/>
@@ -52870,7 +52974,7 @@
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>negative</t>
+          <t>aspiration</t>
         </is>
       </c>
       <c r="J204" t="n">
@@ -52878,12 +52982,12 @@
       </c>
       <c r="K204" t="inlineStr">
         <is>
-          <t>concern</t>
+          <t>hope_or_urgent_public_request</t>
         </is>
       </c>
       <c r="L204" t="inlineStr">
         <is>
-          <t>critical_or_concern</t>
+          <t>public_expectation_or_action_request</t>
         </is>
       </c>
       <c r="M204" t="inlineStr">
@@ -52893,12 +52997,12 @@
       </c>
       <c r="N204" t="inlineStr">
         <is>
-          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Program lapangan &amp; daerah; Pertanyaan publik</t>
+          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Program lapangan &amp; daerah; Aspirasi &amp; permintaan tindak lanjut; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O204" t="inlineStr">
         <is>
-          <t>deforestation_criticism; unanswered_question</t>
+          <t>deforestation_criticism; public_aspiration_needs_response; unanswered_question</t>
         </is>
       </c>
       <c r="P204" t="b">
@@ -52929,7 +53033,7 @@
       </c>
       <c r="X204" t="inlineStr">
         <is>
-          <t>negative</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -52997,7 +53101,7 @@
       </c>
       <c r="N205" t="inlineStr">
         <is>
-          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Program lapangan &amp; daerah; Pertanyaan publik</t>
+          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Program lapangan &amp; daerah; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O205" t="inlineStr">
@@ -53080,7 +53184,7 @@
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>question</t>
+          <t>aspiration</t>
         </is>
       </c>
       <c r="J206" t="n">
@@ -53088,12 +53192,12 @@
       </c>
       <c r="K206" t="inlineStr">
         <is>
-          <t>curiosity_or_help_request</t>
+          <t>hope_or_urgent_public_request</t>
         </is>
       </c>
       <c r="L206" t="inlineStr">
         <is>
-          <t>question_or_information_seeking</t>
+          <t>public_expectation_or_action_request</t>
         </is>
       </c>
       <c r="M206" t="inlineStr">
@@ -53103,12 +53207,12 @@
       </c>
       <c r="N206" t="inlineStr">
         <is>
-          <t>Edukasi FOLU Net Sink 2030; Pertanyaan publik</t>
+          <t>Edukasi FOLU Net Sink 2030; Aspirasi &amp; permintaan tindak lanjut; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O206" t="inlineStr">
         <is>
-          <t>unanswered_question</t>
+          <t>public_aspiration_needs_response; unanswered_question</t>
         </is>
       </c>
       <c r="P206" t="b">
@@ -53209,7 +53313,7 @@
       </c>
       <c r="N207" t="inlineStr">
         <is>
-          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Program lapangan &amp; daerah; Pertanyaan publik</t>
+          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Program lapangan &amp; daerah; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O207" t="inlineStr">
@@ -53313,7 +53417,7 @@
       </c>
       <c r="N208" t="inlineStr">
         <is>
-          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Perhutanan sosial &amp; ekonomi karbon; Program lapangan &amp; daerah; Dukungan &amp; apresiasi; Pertanyaan publik</t>
+          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Perhutanan sosial &amp; ekonomi karbon; Program lapangan &amp; daerah; Dukungan &amp; apresiasi; Aspirasi &amp; permintaan tindak lanjut; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O208" t="inlineStr"/>
@@ -53413,7 +53517,7 @@
       </c>
       <c r="N209" t="inlineStr">
         <is>
-          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Perhutanan sosial &amp; ekonomi karbon; Program lapangan &amp; daerah; Dukungan &amp; apresiasi; Pertanyaan publik</t>
+          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Perhutanan sosial &amp; ekonomi karbon; Program lapangan &amp; daerah; Dukungan &amp; apresiasi; Aspirasi &amp; permintaan tindak lanjut; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O209" t="inlineStr"/>
@@ -53513,7 +53617,7 @@
       </c>
       <c r="N210" t="inlineStr">
         <is>
-          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Perhutanan sosial &amp; ekonomi karbon; Program lapangan &amp; daerah; Dukungan &amp; apresiasi; Pertanyaan publik</t>
+          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Perhutanan sosial &amp; ekonomi karbon; Program lapangan &amp; daerah; Dukungan &amp; apresiasi; Aspirasi &amp; permintaan tindak lanjut; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O210" t="inlineStr"/>
@@ -53598,12 +53702,12 @@
       </c>
       <c r="K211" t="inlineStr">
         <is>
-          <t>curiosity_or_help_request</t>
+          <t>curiosity</t>
         </is>
       </c>
       <c r="L211" t="inlineStr">
         <is>
-          <t>question_or_information_seeking</t>
+          <t>technical_question_or_information_seeking</t>
         </is>
       </c>
       <c r="M211" t="inlineStr">
@@ -53613,7 +53717,7 @@
       </c>
       <c r="N211" t="inlineStr">
         <is>
-          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Perhutanan sosial &amp; ekonomi karbon; Program lapangan &amp; daerah; Dukungan &amp; apresiasi; Pertanyaan publik</t>
+          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Perhutanan sosial &amp; ekonomi karbon; Program lapangan &amp; daerah; Dukungan &amp; apresiasi; Aspirasi &amp; permintaan tindak lanjut; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O211" t="inlineStr">
@@ -53704,12 +53808,12 @@
       </c>
       <c r="K212" t="inlineStr">
         <is>
-          <t>curiosity_or_help_request</t>
+          <t>curiosity</t>
         </is>
       </c>
       <c r="L212" t="inlineStr">
         <is>
-          <t>question_or_information_seeking</t>
+          <t>technical_question_or_information_seeking</t>
         </is>
       </c>
       <c r="M212" t="inlineStr">
@@ -53719,7 +53823,7 @@
       </c>
       <c r="N212" t="inlineStr">
         <is>
-          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Perhutanan sosial &amp; ekonomi karbon; Program lapangan &amp; daerah; Dukungan &amp; apresiasi; Pertanyaan publik</t>
+          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Perhutanan sosial &amp; ekonomi karbon; Program lapangan &amp; daerah; Dukungan &amp; apresiasi; Aspirasi &amp; permintaan tindak lanjut; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O212" t="inlineStr">
@@ -53823,7 +53927,7 @@
       </c>
       <c r="N213" t="inlineStr">
         <is>
-          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Perhutanan sosial &amp; ekonomi karbon; Program lapangan &amp; daerah; Dukungan &amp; apresiasi; Pertanyaan publik</t>
+          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Perhutanan sosial &amp; ekonomi karbon; Program lapangan &amp; daerah; Dukungan &amp; apresiasi; Aspirasi &amp; permintaan tindak lanjut; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O213" t="inlineStr"/>
@@ -54012,12 +54116,12 @@
       </c>
       <c r="K215" t="inlineStr">
         <is>
-          <t>curiosity_or_help_request</t>
+          <t>curiosity</t>
         </is>
       </c>
       <c r="L215" t="inlineStr">
         <is>
-          <t>question_or_information_seeking</t>
+          <t>technical_question_or_information_seeking</t>
         </is>
       </c>
       <c r="M215" t="inlineStr">
@@ -54027,7 +54131,7 @@
       </c>
       <c r="N215" t="inlineStr">
         <is>
-          <t>Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Pertanyaan publik</t>
+          <t>Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O215" t="inlineStr">
@@ -54110,7 +54214,7 @@
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t>question</t>
+          <t>aspiration</t>
         </is>
       </c>
       <c r="J216" t="n">
@@ -54118,12 +54222,12 @@
       </c>
       <c r="K216" t="inlineStr">
         <is>
-          <t>curiosity_or_help_request</t>
+          <t>hope_or_urgent_public_request</t>
         </is>
       </c>
       <c r="L216" t="inlineStr">
         <is>
-          <t>question_or_information_seeking</t>
+          <t>public_expectation_or_action_request</t>
         </is>
       </c>
       <c r="M216" t="inlineStr">
@@ -54133,10 +54237,14 @@
       </c>
       <c r="N216" t="inlineStr">
         <is>
-          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi</t>
-        </is>
-      </c>
-      <c r="O216" t="inlineStr"/>
+          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Aspirasi &amp; permintaan tindak lanjut</t>
+        </is>
+      </c>
+      <c r="O216" t="inlineStr">
+        <is>
+          <t>public_aspiration_needs_response</t>
+        </is>
+      </c>
       <c r="P216" t="b">
         <v>0</v>
       </c>
@@ -54235,7 +54343,7 @@
       </c>
       <c r="N217" t="inlineStr">
         <is>
-          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Pertanyaan publik</t>
+          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O217" t="inlineStr">
@@ -54341,7 +54449,7 @@
       </c>
       <c r="N218" t="inlineStr">
         <is>
-          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Program lapangan &amp; daerah; Pertanyaan publik</t>
+          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Program lapangan &amp; daerah; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O218" t="inlineStr">
@@ -54432,12 +54540,12 @@
       </c>
       <c r="K219" t="inlineStr">
         <is>
-          <t>curiosity_or_help_request</t>
+          <t>curiosity</t>
         </is>
       </c>
       <c r="L219" t="inlineStr">
         <is>
-          <t>question_or_information_seeking</t>
+          <t>technical_question_or_information_seeking</t>
         </is>
       </c>
       <c r="M219" t="inlineStr">
@@ -54447,7 +54555,7 @@
       </c>
       <c r="N219" t="inlineStr">
         <is>
-          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Pertanyaan publik</t>
+          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O219" t="inlineStr">
@@ -54553,7 +54661,7 @@
       </c>
       <c r="N220" t="inlineStr">
         <is>
-          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Program lapangan &amp; daerah; Pertanyaan publik</t>
+          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Program lapangan &amp; daerah; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O220" t="inlineStr">
@@ -54642,12 +54750,12 @@
       </c>
       <c r="K221" t="inlineStr">
         <is>
-          <t>curiosity_or_help_request</t>
+          <t>curiosity</t>
         </is>
       </c>
       <c r="L221" t="inlineStr">
         <is>
-          <t>question_or_information_seeking</t>
+          <t>technical_question_or_information_seeking</t>
         </is>
       </c>
       <c r="M221" t="inlineStr">
@@ -54657,7 +54765,7 @@
       </c>
       <c r="N221" t="inlineStr">
         <is>
-          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Pertanyaan publik</t>
+          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O221" t="inlineStr">
@@ -54738,7 +54846,7 @@
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t>negative</t>
+          <t>aspiration</t>
         </is>
       </c>
       <c r="J222" t="n">
@@ -54746,12 +54854,12 @@
       </c>
       <c r="K222" t="inlineStr">
         <is>
-          <t>concern</t>
+          <t>hope_or_urgent_public_request</t>
         </is>
       </c>
       <c r="L222" t="inlineStr">
         <is>
-          <t>critical_or_concern</t>
+          <t>public_expectation_or_action_request</t>
         </is>
       </c>
       <c r="M222" t="inlineStr">
@@ -54761,12 +54869,12 @@
       </c>
       <c r="N222" t="inlineStr">
         <is>
-          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Program lapangan &amp; daerah; Pertanyaan publik</t>
+          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Program lapangan &amp; daerah; Aspirasi &amp; permintaan tindak lanjut; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O222" t="inlineStr">
         <is>
-          <t>deforestation_criticism; unanswered_question</t>
+          <t>deforestation_criticism; public_aspiration_needs_response; unanswered_question</t>
         </is>
       </c>
       <c r="P222" t="b">
@@ -54797,7 +54905,7 @@
       </c>
       <c r="X222" t="inlineStr">
         <is>
-          <t>negative</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -54865,7 +54973,7 @@
       </c>
       <c r="N223" t="inlineStr">
         <is>
-          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Pertanyaan publik</t>
+          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O223" t="inlineStr">
@@ -54969,7 +55077,7 @@
       </c>
       <c r="N224" t="inlineStr">
         <is>
-          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Program lapangan &amp; daerah; Pertanyaan publik</t>
+          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Program lapangan &amp; daerah; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O224" t="inlineStr">
@@ -55050,7 +55158,7 @@
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t>question</t>
+          <t>aspiration</t>
         </is>
       </c>
       <c r="J225" t="n">
@@ -55058,12 +55166,12 @@
       </c>
       <c r="K225" t="inlineStr">
         <is>
-          <t>curiosity_or_help_request</t>
+          <t>hope_or_urgent_public_request</t>
         </is>
       </c>
       <c r="L225" t="inlineStr">
         <is>
-          <t>question_or_information_seeking</t>
+          <t>public_expectation_or_action_request</t>
         </is>
       </c>
       <c r="M225" t="inlineStr">
@@ -55073,12 +55181,12 @@
       </c>
       <c r="N225" t="inlineStr">
         <is>
-          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Pertanyaan publik</t>
+          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Aspirasi &amp; permintaan tindak lanjut; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O225" t="inlineStr">
         <is>
-          <t>unanswered_question</t>
+          <t>public_aspiration_needs_response; unanswered_question</t>
         </is>
       </c>
       <c r="P225" t="b">
@@ -55177,7 +55285,7 @@
       </c>
       <c r="N226" t="inlineStr">
         <is>
-          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Pertanyaan publik</t>
+          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Aspirasi &amp; permintaan tindak lanjut; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O226" t="inlineStr"/>
@@ -55279,7 +55387,7 @@
       </c>
       <c r="N227" t="inlineStr">
         <is>
-          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Pertanyaan publik</t>
+          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Aspirasi &amp; permintaan tindak lanjut; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O227" t="inlineStr"/>
@@ -55379,7 +55487,7 @@
       </c>
       <c r="N228" t="inlineStr">
         <is>
-          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Pertanyaan publik</t>
+          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Aspirasi &amp; permintaan tindak lanjut; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O228" t="inlineStr"/>
@@ -55481,7 +55589,7 @@
       </c>
       <c r="N229" t="inlineStr">
         <is>
-          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Pertanyaan publik</t>
+          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Aspirasi &amp; permintaan tindak lanjut; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O229" t="inlineStr"/>
@@ -55583,7 +55691,7 @@
       </c>
       <c r="N230" t="inlineStr">
         <is>
-          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Program lapangan &amp; daerah; Pertanyaan publik</t>
+          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Program lapangan &amp; daerah; Aspirasi &amp; permintaan tindak lanjut; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O230" t="inlineStr">
@@ -55689,7 +55797,7 @@
       </c>
       <c r="N231" t="inlineStr">
         <is>
-          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Program lapangan &amp; daerah; Pertanyaan publik</t>
+          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Program lapangan &amp; daerah; Aspirasi &amp; permintaan tindak lanjut; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O231" t="inlineStr">
@@ -55793,7 +55901,7 @@
       </c>
       <c r="N232" t="inlineStr">
         <is>
-          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Pertanyaan publik</t>
+          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O232" t="inlineStr"/>
@@ -55893,7 +56001,7 @@
       </c>
       <c r="N233" t="inlineStr">
         <is>
-          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Dukungan &amp; apresiasi; Pertanyaan publik</t>
+          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Dukungan &amp; apresiasi; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O233" t="inlineStr"/>
@@ -55993,7 +56101,7 @@
       </c>
       <c r="N234" t="inlineStr">
         <is>
-          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Program lapangan &amp; daerah; Pertanyaan publik</t>
+          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Program lapangan &amp; daerah; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O234" t="inlineStr">
@@ -56074,7 +56182,7 @@
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t>question</t>
+          <t>aspiration</t>
         </is>
       </c>
       <c r="J235" t="n">
@@ -56082,12 +56190,12 @@
       </c>
       <c r="K235" t="inlineStr">
         <is>
-          <t>curiosity_or_help_request</t>
+          <t>hope_or_urgent_public_request</t>
         </is>
       </c>
       <c r="L235" t="inlineStr">
         <is>
-          <t>question_or_information_seeking</t>
+          <t>public_expectation_or_action_request</t>
         </is>
       </c>
       <c r="M235" t="inlineStr">
@@ -56097,10 +56205,14 @@
       </c>
       <c r="N235" t="inlineStr">
         <is>
-          <t>Edukasi FOLU Net Sink 2030</t>
-        </is>
-      </c>
-      <c r="O235" t="inlineStr"/>
+          <t>Edukasi FOLU Net Sink 2030; Aspirasi &amp; permintaan tindak lanjut</t>
+        </is>
+      </c>
+      <c r="O235" t="inlineStr">
+        <is>
+          <t>public_aspiration_needs_response</t>
+        </is>
+      </c>
       <c r="P235" t="b">
         <v>0</v>
       </c>
@@ -56199,7 +56311,7 @@
       </c>
       <c r="N236" t="inlineStr">
         <is>
-          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Program lapangan &amp; daerah; Pertanyaan publik</t>
+          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Program lapangan &amp; daerah; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O236" t="inlineStr">
@@ -56303,7 +56415,7 @@
       </c>
       <c r="N237" t="inlineStr">
         <is>
-          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Pertanyaan publik</t>
+          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Aspirasi &amp; permintaan tindak lanjut; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O237" t="inlineStr">
@@ -56386,7 +56498,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>145</v>
+        <v>148</v>
       </c>
     </row>
     <row r="3">
@@ -56401,7 +56513,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4">
@@ -56431,7 +56543,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6">
@@ -56461,7 +56573,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8">
@@ -56491,7 +56603,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -56552,7 +56664,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
     </row>
     <row r="3">
@@ -56567,33 +56679,33 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Deforestasi &amp; tata kelola hutan</t>
+          <t>Edukasi FOLU Net Sink 2030</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>positive</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Edukasi FOLU Net Sink 2030</t>
+          <t>Deforestasi &amp; tata kelola hutan</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>positive</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -56627,18 +56739,18 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Deforestasi &amp; tata kelola hutan</t>
+          <t>Konflik lahan &amp; hutan lindung</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>negative</t>
+          <t>positive</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -56648,22 +56760,22 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Konflik lahan &amp; hutan lindung</t>
+          <t>Deforestasi &amp; tata kelola hutan</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>positive</t>
+          <t>negative</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Pertanyaan publik</t>
+          <t>Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -56746,7 +56858,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56799,7 +56911,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>deforestation_criticism</t>
+          <t>public_aspiration_needs_response</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -56808,22 +56920,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>unanswered_question</t>
+          <t>deforestation_criticism</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Instagram</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6">
@@ -56834,17 +56946,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>YouTube</t>
+          <t>Instagram</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>deforestation_criticism</t>
+          <t>unanswered_question</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -56853,13 +56965,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>conflict_land_tenure</t>
+          <t>deforestation_criticism</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -56868,7 +56980,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -56889,22 +57001,22 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>conflict_land_tenure</t>
+          <t>public_aspiration_needs_response</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Instagram</t>
+          <t>YouTube</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>climate_impact_concern</t>
+          <t>conflict_land_tenure</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -56913,7 +57025,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -56924,7 +57036,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Instagram</t>
+          <t>YouTube</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -56934,15 +57046,45 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>conflict_land_tenure</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>climate_impact_concern</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>deforestation_criticism</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>Instagram</t>
         </is>
       </c>
-      <c r="C13" t="n">
+      <c r="C15" t="n">
         <v>1</v>
       </c>
     </row>
@@ -56957,7 +57099,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA22"/>
+  <dimension ref="A1:AA25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57138,7 +57280,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>question</t>
+          <t>aspiration</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -57146,12 +57288,12 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>curiosity_or_help_request</t>
+          <t>hope_or_urgent_public_request</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>question_or_information_seeking</t>
+          <t>public_expectation_or_action_request</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -57161,12 +57303,12 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Edukasi FOLU Net Sink 2030; Pertanyaan publik</t>
+          <t>Edukasi FOLU Net Sink 2030; Aspirasi &amp; permintaan tindak lanjut; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>unanswered_question</t>
+          <t>public_aspiration_needs_response; unanswered_question</t>
         </is>
       </c>
       <c r="P2" t="b">
@@ -57253,7 +57395,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>question</t>
+          <t>aspiration</t>
         </is>
       </c>
       <c r="J3" t="n">
@@ -57261,12 +57403,12 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>curiosity_or_help_request</t>
+          <t>hope_or_urgent_public_request</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>question_or_information_seeking</t>
+          <t>public_expectation_or_action_request</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -57276,10 +57418,14 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Edukasi FOLU Net Sink 2030</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr"/>
+          <t>Edukasi FOLU Net Sink 2030; Aspirasi &amp; permintaan tindak lanjut</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>public_aspiration_needs_response</t>
+        </is>
+      </c>
       <c r="P3" t="b">
         <v>0</v>
       </c>
@@ -57320,7 +57466,7 @@
         <v>2</v>
       </c>
       <c r="AA3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -57341,22 +57487,22 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">#deforestasiindonesia #deforestasi #folunetsink2030 #kawasanhutan #desamandiangin #desadosan #rantaubertuah #siaksriindrapura #afnisiak #kawankitoafni </t>
+          <t xml:space="preserve">Sobat Hijau, sadar gak sih cuaca makin random? Lagi panas nyengat, tiba-tiba hujan nggak kenal waktu😔 Ternyata semua itu ada hubungannya sama emisi yang terus naik. Simak penjelasannya di video berikut ini, ya! #FOLUNetSink2030 #Kemenhut </t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2023-07-04 04:56:27</t>
+          <t>2026-01-12 11:12:54</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>user_9a98e08bb9</t>
+          <t>user_93f3f7f81c</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>ibu tolong donk carikan solusi buat kampung saya yang hutan bakaux di tebang dan di buat empang</t>
+          <t>min gajah di mason bali masih ditunggangi,tolong lah mna komitmen kalian😭😭😭masa pemerintahan kalah sma mason</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -57364,33 +57510,37 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>question</t>
+          <t>aspiration</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>curiosity_or_help_request</t>
+          <t>hope_or_urgent_public_request</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>question_or_information_seeking</t>
+          <t>public_expectation_or_action_request</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Konflik lahan &amp; hutan lindung</t>
+          <t>Edukasi FOLU Net Sink 2030</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Program lapangan &amp; daerah</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr"/>
+          <t>Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Aspirasi &amp; permintaan tindak lanjut; Pertanyaan teknis publik</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>public_aspiration_needs_response</t>
+        </is>
+      </c>
       <c r="P4" t="b">
         <v>0</v>
       </c>
@@ -57398,20 +57548,20 @@
         <v>1</v>
       </c>
       <c r="R4" t="n">
-        <v>3490</v>
+        <v>50</v>
       </c>
       <c r="S4" t="n">
-        <v>282</v>
+        <v>15</v>
       </c>
       <c r="T4" t="n">
-        <v>411</v>
+        <v>12</v>
       </c>
       <c r="U4" t="n">
-        <v>80200</v>
+        <v>2260</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@afni.z/video/7241168082918575366</t>
+          <t>https://www.tiktok.com/@kemenhut_ri/video/7594277825205751061</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -57428,10 +57578,10 @@
         <v>1</v>
       </c>
       <c r="Z4" t="n">
-        <v>282</v>
+        <v>15</v>
       </c>
       <c r="AA4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -57457,25 +57607,25 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-01-12 11:12:54</t>
+          <t>2026-01-13 01:44:02</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>user_93f3f7f81c</t>
+          <t>user_666f261600</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>min gajah di mason bali masih ditunggangi,tolong lah mna komitmen kalian😭😭😭masa pemerintahan kalah sma mason</t>
+          <t>Tolong kroscek gajah di Mason park min, ini sudah sangat memperhatin kan</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>question</t>
+          <t>aspiration</t>
         </is>
       </c>
       <c r="J5" t="n">
@@ -57483,12 +57633,12 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>curiosity_or_help_request</t>
+          <t>hope_or_urgent_public_request</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>question_or_information_seeking</t>
+          <t>public_expectation_or_action_request</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -57498,10 +57648,14 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Pertanyaan publik</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr"/>
+          <t>Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Aspirasi &amp; permintaan tindak lanjut; Pertanyaan teknis publik</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>public_aspiration_needs_response</t>
+        </is>
+      </c>
       <c r="P5" t="b">
         <v>0</v>
       </c>
@@ -57542,7 +57696,7 @@
         <v>15</v>
       </c>
       <c r="AA5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -57563,77 +57717,79 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sobat Hijau, sadar gak sih cuaca makin random? Lagi panas nyengat, tiba-tiba hujan nggak kenal waktu😔 Ternyata semua itu ada hubungannya sama emisi yang terus naik. Simak penjelasannya di video berikut ini, ya! #FOLUNetSink2030 #Kemenhut </t>
+          <t xml:space="preserve">“FOLU itu apa sih?” 🤔 Kira-kira Sobat Hijau sudah tau belum ya? Di video ini, kita rangkum reaksi netizen soal FOLU 😉 Lewat video ini, kita bahas kenapa FOLU penting buat kita semua! #FOLUNetSink2030 #Kemenhut </t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-01-13 01:44:02</t>
+          <t>2026-01-17 01:05:37</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>user_666f261600</t>
+          <t>user_b09c5bc8c2</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tolong kroscek gajah di Mason park min, ini sudah sangat memperhatin kan</t>
+          <t>tolong bantu gajah gajah diIndonesia pls jangan tutup mata🥹 Juli Antoni #SAVETESSONILO #SAVEPLGSEBANGA #SAVEPLGSEBLAT #SAVEWAYKAMBAS #SAVEPLGMINASRIAU #SAVEHUTANKALIMANTAN #SAVEHUTANPAPUA #SAVEWILDLIFE #SAVEHUTANINDONESIA #STOPDEFORESTASI #KAMIBERSAMAPARASATWAINDONESIA</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>question</t>
+          <t>aspiration</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>curiosity_or_help_request</t>
+          <t>hope_or_urgent_public_request</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>question_or_information_seeking</t>
+          <t>public_expectation_or_action_request</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Edukasi FOLU Net Sink 2030</t>
+          <t>Deforestasi &amp; tata kelola hutan</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Pertanyaan publik</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr"/>
+          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Program lapangan &amp; daerah; Aspirasi &amp; permintaan tindak lanjut; Pertanyaan teknis publik</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>deforestation_criticism; public_aspiration_needs_response; unanswered_question</t>
+        </is>
+      </c>
       <c r="P6" t="b">
         <v>0</v>
       </c>
-      <c r="Q6" t="n">
-        <v>1</v>
-      </c>
+      <c r="Q6" t="inlineStr"/>
       <c r="R6" t="n">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T6" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="U6" t="n">
-        <v>2260</v>
+        <v>1544</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@kemenhut_ri/video/7594277825205751061</t>
+          <t>https://www.tiktok.com/@kemenhut_ri/video/7594755168709725461</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -57647,13 +57803,13 @@
         </is>
       </c>
       <c r="Y6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="AA6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -57674,77 +57830,79 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sobat Hijau, sadar gak sih cuaca makin random? Lagi panas nyengat, tiba-tiba hujan nggak kenal waktu😔 Ternyata semua itu ada hubungannya sama emisi yang terus naik. Simak penjelasannya di video berikut ini, ya! #FOLUNetSink2030 #Kemenhut </t>
+          <t xml:space="preserve">“Perubahan iklim adalah tantangan bersama yang butuh aksi kolektif.” FOLU Net Sink 2030 berfokus pada pengurangan emisi melalui pengelolaan hutan dan penggunaan lahan. Pendekatan ini menempatkan sektor kehutanan sebagai bagian penting dalam strategi pengendalian perubahan iklim. #FOLUNetSink2030 #Kemenhut </t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-01-14 14:27:35</t>
+          <t>2026-01-17 01:04:03</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>user_3570241893</t>
+          <t>user_b09c5bc8c2</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Gajah di Mason tolong perhatiannya. satwa dilindungi bukan dieksploitasi demi uang</t>
+          <t>tolong bantu gajah' diIndonesia pls jangan tutup mata #SAVETESSONILO #SAVEPLGSEBANGA #SAVEPLGSEBLAT #SAVEWAYKAMBAS #SAVEPLGMINASRIAU #SAVEHUTANKALIMANTAN #SAVEHUTANPAPUA #SAVEWILDLIFE #SAVEHUTANINDONESIA #STOPDEFORESTASI #KAMIBERSAMAPARASATWAINDONESIA</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>question</t>
+          <t>aspiration</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>curiosity_or_help_request</t>
+          <t>hope_or_urgent_public_request</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>question_or_information_seeking</t>
+          <t>public_expectation_or_action_request</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Edukasi FOLU Net Sink 2030</t>
+          <t>Konflik lahan &amp; hutan lindung</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Pertanyaan publik</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr"/>
+          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Program lapangan &amp; daerah; Aspirasi &amp; permintaan tindak lanjut; Pertanyaan teknis publik</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>deforestation_criticism; public_aspiration_needs_response; unanswered_question</t>
+        </is>
+      </c>
       <c r="P7" t="b">
         <v>0</v>
       </c>
-      <c r="Q7" t="n">
-        <v>1</v>
-      </c>
+      <c r="Q7" t="inlineStr"/>
       <c r="R7" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="T7" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="U7" t="n">
-        <v>2260</v>
+        <v>1910</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@kemenhut_ri/video/7594277825205751061</t>
+          <t>https://www.tiktok.com/@kemenhut_ri/video/7595875420482833685</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -57758,13 +57916,13 @@
         </is>
       </c>
       <c r="Y7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="AA7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -57785,75 +57943,81 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sobat Hijau, sadar gak sih cuaca makin random? Lagi panas nyengat, tiba-tiba hujan nggak kenal waktu😔 Ternyata semua itu ada hubungannya sama emisi yang terus naik. Simak penjelasannya di video berikut ini, ya! #FOLUNetSink2030 #Kemenhut </t>
+          <t xml:space="preserve">#deforestasiindonesia #deforestasi #folunetsink2030 #kawasanhutan #desamandiangin #desadosan #rantaubertuah #siaksriindrapura #afnisiak #kawankitoafni </t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-01-15 05:02:47</t>
+          <t>2023-07-04 04:56:27</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>user_bab2d27c7d</t>
+          <t>user_9a98e08bb9</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>tolong mason elephant park pak banyak gajah di exploitasi, gajah hamil ditunggangi, gajah kecil di tunggangi, luka luka gajah nya , untuk minum mereka susah,, tolong pak</t>
+          <t>ibu tolong donk carikan solusi buat kampung saya yang hutan bakaux di tebang dan di buat empang</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>question</t>
+          <t>aspiration</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>curiosity_or_help_request</t>
+          <t>hope_or_urgent_public_request</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>question_or_information_seeking</t>
+          <t>public_expectation_or_action_request</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Edukasi FOLU Net Sink 2030</t>
+          <t>Konflik lahan &amp; hutan lindung</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Pertanyaan publik</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr"/>
+          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Program lapangan &amp; daerah; Aspirasi &amp; permintaan tindak lanjut</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>public_aspiration_needs_response</t>
+        </is>
+      </c>
       <c r="P8" t="b">
         <v>0</v>
       </c>
-      <c r="Q8" t="inlineStr"/>
+      <c r="Q8" t="n">
+        <v>1</v>
+      </c>
       <c r="R8" t="n">
-        <v>50</v>
+        <v>3490</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>282</v>
       </c>
       <c r="T8" t="n">
-        <v>12</v>
+        <v>411</v>
       </c>
       <c r="U8" t="n">
-        <v>2260</v>
+        <v>80200</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@kemenhut_ri/video/7594277825205751061</t>
+          <t>https://www.tiktok.com/@afni.z/video/7241168082918575366</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
@@ -57867,10 +58031,10 @@
         </is>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z8" t="n">
-        <v>15</v>
+        <v>282</v>
       </c>
       <c r="AA8" t="n">
         <v>2</v>
@@ -57884,7 +58048,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>YouTube</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -57894,84 +58058,102 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>FOLU TALK: Jaga Hutan, Dapat Manfaat. Mengenal Result Based Payment lebih dekat.</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr"/>
+          <t xml:space="preserve">Sobat Hijau, sadar gak sih cuaca makin random? Lagi panas nyengat, tiba-tiba hujan nggak kenal waktu😔 Ternyata semua itu ada hubungannya sama emisi yang terus naik. Simak penjelasannya di video berikut ini, ya! #FOLUNetSink2030 #Kemenhut </t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>2026-01-14 14:27:35</t>
+        </is>
+      </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>user_876150114f</t>
+          <t>user_3570241893</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Di tempat kami hutan habiz d babat pembalakn liar pak,,airterjun objek wisata d tempat kami yg biasanya airnya besar sekr sudah kecil sekali karena penebang liar ...saya ingin sekali menghijaukan kembali hutan kami pak ,,mohon bantuannya pak ,,sebelum semua daerah kami d gunduli penebang liar 👏👏</t>
+          <t>Gajah di Mason tolong perhatiannya. satwa dilindungi bukan dieksploitasi demi uang</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>negative</t>
+          <t>aspiration</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>concern</t>
+          <t>hope_or_urgent_public_request</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>critical_or_concern</t>
+          <t>public_expectation_or_action_request</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Deforestasi &amp; tata kelola hutan</t>
+          <t>Edukasi FOLU Net Sink 2030</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Pertanyaan publik</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr"/>
+          <t>Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Aspirasi &amp; permintaan tindak lanjut; Pertanyaan teknis publik</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>public_aspiration_needs_response</t>
+        </is>
+      </c>
       <c r="P9" t="b">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" t="inlineStr"/>
-      <c r="S9" t="inlineStr"/>
-      <c r="T9" t="inlineStr"/>
-      <c r="U9" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="R9" t="n">
+        <v>50</v>
+      </c>
+      <c r="S9" t="n">
+        <v>15</v>
+      </c>
+      <c r="T9" t="n">
+        <v>12</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2260</v>
+      </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=UZBbIeLsnMI</t>
+          <t>https://www.tiktok.com/@kemenhut_ri/video/7594277825205751061</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>youtube_kemenhut_folu_14_comments_title_date.csv</t>
+          <t>tiktok_folu_comments_final.csv</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>negative</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA9" t="inlineStr"/>
+        <v>15</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -58037,7 +58219,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Pertanyaan publik</t>
+          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -58094,7 +58276,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Instagram</t>
+          <t>YouTube</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -58104,26 +58286,22 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Youth Act: Forest Fire Control</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>2025-12-05 00:31:56 +0000</t>
-        </is>
-      </c>
+          <t>FOLU Talks: The Future Of Industrial Plantation Forest in Contributing to Renewable Energy.</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>user_27f6241d18</t>
+          <t>user_bc0e89bf21</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Agro forestri, paru2 sehat, lahan subur bebas dari ancaman bencana</t>
+          <t>Kementerian kehutanan membiarkan pembalakan liar di Wawoni island Sulawesi Tenggara parah</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -58145,39 +58323,33 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Konflik lahan &amp; hutan lindung</t>
+          <t>Deforestasi &amp; tata kelola hutan</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Konflik lahan &amp; hutan lindung; Perubahan iklim &amp; emisi</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>conflict_land_tenure; climate_impact_concern</t>
-        </is>
-      </c>
+          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr"/>
       <c r="P11" t="b">
         <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
-      <c r="R11" t="n">
-        <v>788</v>
-      </c>
+      <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr"/>
       <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DM7UqqPvdw6/</t>
+          <t>https://www.youtube.com/watch?v=VAWbmpRDDeM</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>instagram_kemenhut_folu_talks_deep_comments.csv</t>
+          <t>youtube_kemenhut_folu_14_comments_title_date.csv</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -58201,7 +58373,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>YouTube</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -58211,18 +58383,22 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>FOLU Talks: The Future Of Industrial Plantation Forest in Contributing to Renewable Energy.</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr"/>
+          <t xml:space="preserve">“FOLU itu apa sih?” 🤔 Kira-kira Sobat Hijau sudah tau belum ya? Di video ini, kita rangkum reaksi netizen soal FOLU 😉 Lewat video ini, kita bahas kenapa FOLU penting buat kita semua! #FOLUNetSink2030 #Kemenhut </t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>2026-01-13 16:32:31</t>
+        </is>
+      </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>user_bc0e89bf21</t>
+          <t>user_df09085471</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Kementerian kehutanan membiarkan pembalakan liar di Wawoni island Sulawesi Tenggara parah</t>
+          <t>#SAVETESSONILO #SAVEPLGSEBANGA #SAVEPLGSEBLAT #SAVEWAYKAMBAS #SAVEPLGMINASRIAU #SAVEHUTANKALIMANTAN #SAVEHUTANPAPUA #SAVEWILDLIFE #SAVEHUTANINDONESIA #STOPDEFORESTASI #KAMIBERSAMAPARASATWAINDONESIA</t>
         </is>
       </c>
       <c r="H12" t="n">
@@ -58234,7 +58410,7 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -58253,28 +58429,40 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr"/>
+          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Program lapangan &amp; daerah; Pertanyaan teknis publik</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>deforestation_criticism; unanswered_question</t>
+        </is>
+      </c>
       <c r="P12" t="b">
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" t="inlineStr"/>
-      <c r="S12" t="inlineStr"/>
-      <c r="T12" t="inlineStr"/>
-      <c r="U12" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="R12" t="n">
+        <v>34</v>
+      </c>
+      <c r="S12" t="n">
+        <v>9</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1544</v>
+      </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=VAWbmpRDDeM</t>
+          <t>https://www.tiktok.com/@kemenhut_ri/video/7594755168709725461</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>youtube_kemenhut_folu_14_comments_title_date.csv</t>
+          <t>tiktok_folu_comments_final.csv</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -58283,10 +58471,10 @@
         </is>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AA12" t="inlineStr"/>
     </row>
@@ -58308,26 +58496,26 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">“FOLU itu apa sih?” 🤔 Kira-kira Sobat Hijau sudah tau belum ya? Di video ini, kita rangkum reaksi netizen soal FOLU 😉 Lewat video ini, kita bahas kenapa FOLU penting buat kita semua! #FOLUNetSink2030 #Kemenhut </t>
+          <t xml:space="preserve">#deforestasiindonesia #deforestasi #folunetsink2030 #kawasanhutan #desamandiangin #desadosan #rantaubertuah #siaksriindrapura #afnisiak #kawankitoafni </t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-01-13 16:32:31</t>
+          <t>2023-07-20 10:47:28</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>user_df09085471</t>
+          <t>user_208f57a349</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>#SAVETESSONILO #SAVEPLGSEBANGA #SAVEPLGSEBLAT #SAVEWAYKAMBAS #SAVEPLGMINASRIAU #SAVEHUTANKALIMANTAN #SAVEHUTANPAPUA #SAVEWILDLIFE #SAVEHUTANINDONESIA #STOPDEFORESTASI #KAMIBERSAMAPARASATWAINDONESIA</t>
+          <t>hutan untuk perusahaan.</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -58349,40 +58537,40 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Deforestasi &amp; tata kelola hutan</t>
+          <t>Konflik lahan &amp; hutan lindung</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Program lapangan &amp; daerah; Pertanyaan publik</t>
+          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Program lapangan &amp; daerah</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>deforestation_criticism; unanswered_question</t>
+          <t>conflict_land_tenure</t>
         </is>
       </c>
       <c r="P13" t="b">
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R13" t="n">
-        <v>34</v>
+        <v>3490</v>
       </c>
       <c r="S13" t="n">
-        <v>9</v>
+        <v>282</v>
       </c>
       <c r="T13" t="n">
-        <v>2</v>
+        <v>411</v>
       </c>
       <c r="U13" t="n">
-        <v>1544</v>
+        <v>80200</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@kemenhut_ri/video/7594755168709725461</t>
+          <t>https://www.tiktok.com/@afni.z/video/7241168082918575366</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
@@ -58396,10 +58584,10 @@
         </is>
       </c>
       <c r="Y13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z13" t="n">
-        <v>9</v>
+        <v>282</v>
       </c>
       <c r="AA13" t="inlineStr"/>
     </row>
@@ -58426,21 +58614,21 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2023-07-20 10:47:28</t>
+          <t>2023-06-11 02:05:15</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>user_208f57a349</t>
+          <t>user_feb2453f53</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>hutan untuk perusahaan.</t>
+          <t>iya perusahaan lebih besar buk</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -58478,9 +58666,7 @@
       <c r="P14" t="b">
         <v>0</v>
       </c>
-      <c r="Q14" t="n">
-        <v>1</v>
-      </c>
+      <c r="Q14" t="inlineStr"/>
       <c r="R14" t="n">
         <v>3490</v>
       </c>
@@ -58509,7 +58695,7 @@
         </is>
       </c>
       <c r="Y14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
         <v>282</v>
@@ -58580,7 +58766,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Deforestasi &amp; tata kelola hutan; Dukungan &amp; apresiasi; Pertanyaan publik</t>
+          <t>Deforestasi &amp; tata kelola hutan; Dukungan &amp; apresiasi; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O15" t="inlineStr"/>
@@ -59008,7 +59194,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Dukungan &amp; apresiasi; Pertanyaan publik</t>
+          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perubahan iklim &amp; emisi; Dukungan &amp; apresiasi; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O19" t="inlineStr"/>
@@ -59214,7 +59400,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>Edukasi FOLU Net Sink 2030; Dukungan &amp; apresiasi; Pertanyaan publik</t>
+          <t>Edukasi FOLU Net Sink 2030; Dukungan &amp; apresiasi; Pertanyaan teknis publik</t>
         </is>
       </c>
       <c r="O21" t="inlineStr"/>
@@ -59274,25 +59460,25 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2023-06-05 13:00:31</t>
+          <t>2023-06-06 14:56:23</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>user_29ad6df2e8</t>
+          <t>user_2e459c565f</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Ibu Afni IDOLAKUUUUU, org Siak untuk masyarakat SIAK.. 😍😍😍</t>
+          <t>Boleh ajukan tp blm tentu di setujui</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>positive</t>
+          <t>question</t>
         </is>
       </c>
       <c r="J22" t="n">
@@ -59300,12 +59486,12 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>appreciation</t>
+          <t>curiosity</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>supportive_or_appreciative</t>
+          <t>technical_question_or_information_seeking</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -59315,15 +59501,19 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Perhutanan sosial &amp; ekonomi karbon; Program lapangan &amp; daerah; Dukungan &amp; apresiasi</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr"/>
+          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Program lapangan &amp; daerah; Pertanyaan teknis publik</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>unanswered_question</t>
+        </is>
+      </c>
       <c r="P22" t="b">
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R22" t="n">
         <v>3490</v>
@@ -59349,16 +59539,351 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>positive</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="Y22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z22" t="n">
         <v>282</v>
       </c>
       <c r="AA22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>public_social_comment</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>TikTok</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#deforestasiindonesia #deforestasi #folunetsink2030 #kawasanhutan #desamandiangin #desadosan #rantaubertuah #siaksriindrapura #afnisiak #kawankitoafni </t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>2023-06-14 18:02:47</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>user_31fc8e716a</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>buk, kampung saya komplik kawasan dengan taman nasional, kampung kami sudah di klaim masuk dalam kawasan, ada solusi buk?</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>19</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>question</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>1</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>curiosity</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>technical_question_or_information_seeking</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>Konflik lahan &amp; hutan lindung</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Program lapangan &amp; daerah; Pertanyaan teknis publik</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>unanswered_question</t>
+        </is>
+      </c>
+      <c r="P23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="n">
+        <v>3490</v>
+      </c>
+      <c r="S23" t="n">
+        <v>282</v>
+      </c>
+      <c r="T23" t="n">
+        <v>411</v>
+      </c>
+      <c r="U23" t="n">
+        <v>80200</v>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@afni.z/video/7241168082918575366</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>tiktok_folu_comments_final.csv</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="Y23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>282</v>
+      </c>
+      <c r="AA23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>public_social_comment</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>TikTok</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#deforestasiindonesia #deforestasi #folunetsink2030 #kawasanhutan #desamandiangin #desadosan #rantaubertuah #siaksriindrapura #afnisiak #kawankitoafni </t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>2023-07-03 11:50:16</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>user_36ad622369</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>gk percaya bagaimana dengan IKN</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>5</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>question</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>1</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>curiosity</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>technical_question_or_information_seeking</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>Deforestasi &amp; tata kelola hutan</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Program lapangan &amp; daerah; Pertanyaan teknis publik</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>unanswered_question</t>
+        </is>
+      </c>
+      <c r="P24" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="n">
+        <v>3490</v>
+      </c>
+      <c r="S24" t="n">
+        <v>282</v>
+      </c>
+      <c r="T24" t="n">
+        <v>411</v>
+      </c>
+      <c r="U24" t="n">
+        <v>80200</v>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@afni.z/video/7241168082918575366</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>tiktok_folu_comments_final.csv</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="Y24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>282</v>
+      </c>
+      <c r="AA24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>public_social_comment</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>TikTok</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#deforestasiindonesia #deforestasi #folunetsink2030 #kawasanhutan #desamandiangin #desadosan #rantaubertuah #siaksriindrapura #afnisiak #kawankitoafni </t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>2023-07-14 04:59:55</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>user_e264e5550b</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Dn yg mnciptkn konflik itu ada,siapa .....?? apkh rkyt jelata,pengusaha,negara,apa macan rimba....🙏🙏</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>15</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>question</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>curiosity</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>technical_question_or_information_seeking</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>Konflik lahan &amp; hutan lindung</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>Konflik lahan &amp; hutan lindung; Deforestasi &amp; tata kelola hutan; Edukasi FOLU Net Sink 2030; Program lapangan &amp; daerah; Pertanyaan teknis publik</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>unanswered_question</t>
+        </is>
+      </c>
+      <c r="P25" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>1</v>
+      </c>
+      <c r="R25" t="n">
+        <v>3490</v>
+      </c>
+      <c r="S25" t="n">
+        <v>282</v>
+      </c>
+      <c r="T25" t="n">
+        <v>411</v>
+      </c>
+      <c r="U25" t="n">
+        <v>80200</v>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@afni.z/video/7241168082918575366</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>tiktok_folu_comments_final.csv</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="Y25" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>282</v>
+      </c>
+      <c r="AA25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -59429,7 +59954,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-16 01:32:57 +0700</t>
+          <t>2026-06-16 02:22:15 +0700</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -59451,16 +59976,16 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>{'neutral': 227, 'positive': 53, 'negative': 21}</t>
+          <t>{'neutral': 231, 'positive': 52, 'negative': 18}</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>{'neutral': 162, 'positive': 53, 'negative': 21}</t>
+          <t>{'neutral': 166, 'positive': 52, 'negative': 18}</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>128</v>
+        <v>147</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>

--- a/data/folu_social_listening_report.xlsx
+++ b/data/folu_social_listening_report.xlsx
@@ -59954,7 +59954,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-16 02:22:15 +0700</t>
+          <t>2026-06-16 22:15:17 +0700</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -59989,7 +59989,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>{'instagram': 'BYOB + Instagram API/session scrape available from prior task; comments included.', 'youtube': 'YouTube streams/comments dataset included from prior scrape.', 'tiktok': 'BYOB discovery worked; Obscura attempted but returned blank/eval null on TikTok; fallback extractor/API/session used; comments included.', 'website': 'BYOB verified seeds + Obscura bulk text; zero-byte PPID pages excluded during cleaning.'}</t>
+          <t>{'instagram': 'Post dan komentar publik dinormalisasi dari halaman/reel relevan, termasuk metadata waktu, engagement, caption, dan URL.', 'youtube': 'Komentar dan metadata video disatukan ke skema lintas platform untuk analisis sentiment, topik, dan risk flag.', 'tiktok': 'Metadata post dan komentar diekstrak dari halaman publik, lalu dibersihkan dari duplikasi dan komentar low-information.', 'website': 'Artikel/halaman web relevan dipakai sebagai konteks media discourse; halaman kosong atau tidak valid dikeluarkan saat cleaning.'}</t>
         </is>
       </c>
     </row>
